--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,6 +923,118 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126380574</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91260</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Inre Öreström, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>699818</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7113393</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>126380574</v>
       </c>
       <c r="B4" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126868059</v>
+        <v>126862626</v>
       </c>
       <c r="B5" t="n">
-        <v>91245</v>
+        <v>80114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699956</v>
+        <v>699893</v>
       </c>
       <c r="R5" t="n">
-        <v>7113052</v>
+        <v>7113185</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,12 +1122,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126862626</v>
+        <v>126868059</v>
       </c>
       <c r="B6" t="n">
-        <v>80083</v>
+        <v>91319</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699893</v>
+        <v>699956</v>
       </c>
       <c r="R6" t="n">
-        <v>7113185</v>
+        <v>7113052</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,12 +1223,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1242,7 +1242,7 @@
         <v>126864688</v>
       </c>
       <c r="B7" t="n">
-        <v>82792</v>
+        <v>82852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>126862625</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>126862596</v>
       </c>
       <c r="B9" t="n">
-        <v>99005</v>
+        <v>99080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126850606</v>
+        <v>126868057</v>
       </c>
       <c r="B10" t="n">
-        <v>57817</v>
+        <v>91319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,37 +1554,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nydala, Nydala, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>699845</v>
+        <v>699944</v>
       </c>
       <c r="R10" t="n">
-        <v>7113169</v>
+        <v>7113181</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,60 +1628,64 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Torbjörn Söderquist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126868067</v>
+        <v>126850606</v>
       </c>
       <c r="B11" t="n">
-        <v>98278</v>
+        <v>57817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Nydala, Nydala, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>699947</v>
+        <v>699845</v>
       </c>
       <c r="R11" t="n">
-        <v>7113090</v>
+        <v>7113169</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1711,11 +1715,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca 20 st på liten yta</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,26 +1729,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>126867857</v>
       </c>
       <c r="B12" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,32 +1855,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126868057</v>
+        <v>126868067</v>
       </c>
       <c r="B13" t="n">
-        <v>91245</v>
+        <v>98353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>699944</v>
+        <v>699947</v>
       </c>
       <c r="R13" t="n">
-        <v>7113181</v>
+        <v>7113090</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,6 +1926,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ca 20 st på liten yta</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,7 +1964,7 @@
         <v>126862664</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>126864681</v>
       </c>
       <c r="B15" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126862590</v>
+        <v>126862622</v>
       </c>
       <c r="B16" t="n">
-        <v>57817</v>
+        <v>80114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2174,46 +2174,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>699877</v>
+        <v>699782</v>
       </c>
       <c r="R16" t="n">
-        <v>7113231</v>
+        <v>7113622</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2276,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126862622</v>
+        <v>126862590</v>
       </c>
       <c r="B17" t="n">
-        <v>80083</v>
+        <v>57817</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,34 +2275,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>699782</v>
+        <v>699877</v>
       </c>
       <c r="R17" t="n">
-        <v>7113622</v>
+        <v>7113231</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,45 +2377,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126868062</v>
+        <v>126867850</v>
       </c>
       <c r="B18" t="n">
-        <v>57817</v>
+        <v>98457</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>699845</v>
+        <v>699955</v>
       </c>
       <c r="R18" t="n">
-        <v>7113187</v>
+        <v>7113130</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,12 +2462,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2481,7 +2481,7 @@
         <v>126867848</v>
       </c>
       <c r="B19" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,45 +2579,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126867850</v>
+        <v>126868062</v>
       </c>
       <c r="B20" t="n">
-        <v>98382</v>
+        <v>57817</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>699955</v>
+        <v>699845</v>
       </c>
       <c r="R20" t="n">
-        <v>7113130</v>
+        <v>7113187</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,12 +2664,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2683,7 +2683,7 @@
         <v>126863282</v>
       </c>
       <c r="B21" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126862624</v>
+        <v>126862599</v>
       </c>
       <c r="B22" t="n">
-        <v>80083</v>
+        <v>80115</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2792,21 +2792,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>699857</v>
+        <v>699778</v>
       </c>
       <c r="R22" t="n">
-        <v>7113431</v>
+        <v>7113628</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126862599</v>
+        <v>126864675</v>
       </c>
       <c r="B23" t="n">
-        <v>80084</v>
+        <v>96689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2893,21 +2893,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>699778</v>
+        <v>699913</v>
       </c>
       <c r="R23" t="n">
-        <v>7113628</v>
+        <v>7113203</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2967,12 +2967,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2983,10 +2983,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126864675</v>
+        <v>126862624</v>
       </c>
       <c r="B24" t="n">
-        <v>96614</v>
+        <v>80114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2994,21 +2994,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>699913</v>
+        <v>699857</v>
       </c>
       <c r="R24" t="n">
-        <v>7113203</v>
+        <v>7113431</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3068,12 +3068,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3087,7 +3087,7 @@
         <v>126868058</v>
       </c>
       <c r="B25" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>126862598</v>
       </c>
       <c r="B26" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3286,10 +3286,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126862570</v>
+        <v>126862669</v>
       </c>
       <c r="B27" t="n">
-        <v>105381</v>
+        <v>98353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3297,21 +3297,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221725</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699830</v>
+        <v>699879</v>
       </c>
       <c r="R27" t="n">
-        <v>7113371</v>
+        <v>7113265</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126862669</v>
+        <v>126867894</v>
       </c>
       <c r="B28" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3418,14 +3418,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699879</v>
+        <v>699948</v>
       </c>
       <c r="R28" t="n">
-        <v>7113265</v>
+        <v>7113110</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,12 +3472,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3488,10 +3488,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126862627</v>
+        <v>126862570</v>
       </c>
       <c r="B29" t="n">
-        <v>80119</v>
+        <v>105456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,21 +3499,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>221725</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699788</v>
+        <v>699830</v>
       </c>
       <c r="R29" t="n">
-        <v>7113541</v>
+        <v>7113371</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126867894</v>
+        <v>126862627</v>
       </c>
       <c r="B30" t="n">
-        <v>98278</v>
+        <v>80150</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3600,34 +3600,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699948</v>
+        <v>699788</v>
       </c>
       <c r="R30" t="n">
-        <v>7113110</v>
+        <v>7113541</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3674,12 +3674,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3693,7 +3693,7 @@
         <v>126864689</v>
       </c>
       <c r="B31" t="n">
-        <v>82792</v>
+        <v>82852</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>126867883</v>
       </c>
       <c r="B32" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>126863288</v>
       </c>
       <c r="B33" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>126867886</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4095,10 +4095,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126863291</v>
+        <v>126862623</v>
       </c>
       <c r="B35" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699885</v>
+        <v>699773</v>
       </c>
       <c r="R35" t="n">
-        <v>7113259</v>
+        <v>7113587</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4180,12 +4180,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4297,10 +4297,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126862623</v>
+        <v>126863291</v>
       </c>
       <c r="B37" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699773</v>
+        <v>699885</v>
       </c>
       <c r="R37" t="n">
-        <v>7113587</v>
+        <v>7113259</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,12 +4382,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4401,7 +4401,7 @@
         <v>126867889</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4499,10 +4499,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126868055</v>
+        <v>126862672</v>
       </c>
       <c r="B39" t="n">
-        <v>91210</v>
+        <v>80149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699981</v>
+        <v>699843</v>
       </c>
       <c r="R39" t="n">
-        <v>7113021</v>
+        <v>7113335</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4600,10 +4600,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126862672</v>
+        <v>126868055</v>
       </c>
       <c r="B40" t="n">
-        <v>80118</v>
+        <v>91284</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4611,21 +4611,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699843</v>
+        <v>699981</v>
       </c>
       <c r="R40" t="n">
-        <v>7113335</v>
+        <v>7113021</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4685,12 +4685,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4704,7 +4704,7 @@
         <v>126867887</v>
       </c>
       <c r="B41" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4802,45 +4802,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126867884</v>
+        <v>126862595</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>80143</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699877</v>
+        <v>699848</v>
       </c>
       <c r="R42" t="n">
-        <v>7113569</v>
+        <v>7113330</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4887,12 +4887,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4903,45 +4903,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126862595</v>
+        <v>126867884</v>
       </c>
       <c r="B43" t="n">
-        <v>80112</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699848</v>
+        <v>699877</v>
       </c>
       <c r="R43" t="n">
-        <v>7113330</v>
+        <v>7113569</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4988,12 +4988,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5007,7 +5007,7 @@
         <v>126862628</v>
       </c>
       <c r="B44" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>126862671</v>
       </c>
       <c r="B45" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5206,32 +5206,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126862659</v>
+        <v>126862620</v>
       </c>
       <c r="B46" t="n">
-        <v>75059</v>
+        <v>80114</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5241,10 +5241,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699845</v>
+        <v>699885</v>
       </c>
       <c r="R46" t="n">
-        <v>7113325</v>
+        <v>7113266</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5307,45 +5307,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126862620</v>
+        <v>126867851</v>
       </c>
       <c r="B47" t="n">
-        <v>80083</v>
+        <v>98457</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699885</v>
+        <v>699963</v>
       </c>
       <c r="R47" t="n">
-        <v>7113266</v>
+        <v>7113120</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,12 +5392,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5408,10 +5408,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126867851</v>
+        <v>126862581</v>
       </c>
       <c r="B48" t="n">
-        <v>98382</v>
+        <v>91284</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5419,34 +5419,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>699963</v>
+        <v>699816</v>
       </c>
       <c r="R48" t="n">
-        <v>7113120</v>
+        <v>7113390</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5493,12 +5493,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5509,10 +5509,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126862581</v>
+        <v>126862659</v>
       </c>
       <c r="B49" t="n">
-        <v>91210</v>
+        <v>75118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5520,21 +5520,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>6439</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>699816</v>
+        <v>699845</v>
       </c>
       <c r="R49" t="n">
-        <v>7113390</v>
+        <v>7113325</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5610,10 +5610,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126867890</v>
+        <v>126864677</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>91319</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5621,34 +5621,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>699832</v>
+        <v>699961</v>
       </c>
       <c r="R50" t="n">
-        <v>7113381</v>
+        <v>7113050</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5695,12 +5695,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5711,45 +5711,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126862568</v>
+        <v>126867890</v>
       </c>
       <c r="B51" t="n">
-        <v>105381</v>
+        <v>79011</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>699772</v>
+        <v>699832</v>
       </c>
       <c r="R51" t="n">
-        <v>7113578</v>
+        <v>7113381</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5796,12 +5796,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5812,10 +5812,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126863289</v>
+        <v>126864676</v>
       </c>
       <c r="B52" t="n">
-        <v>97239</v>
+        <v>91284</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5823,21 +5823,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>699799</v>
+        <v>699986</v>
       </c>
       <c r="R52" t="n">
-        <v>7113391</v>
+        <v>7113023</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,12 +5897,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5913,10 +5913,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126864676</v>
+        <v>126863289</v>
       </c>
       <c r="B53" t="n">
-        <v>91210</v>
+        <v>97314</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5924,21 +5924,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>699986</v>
+        <v>699799</v>
       </c>
       <c r="R53" t="n">
-        <v>7113023</v>
+        <v>7113391</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5998,12 +5998,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6014,32 +6014,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126864677</v>
+        <v>126862568</v>
       </c>
       <c r="B54" t="n">
-        <v>91245</v>
+        <v>105456</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6049,10 +6049,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>699961</v>
+        <v>699772</v>
       </c>
       <c r="R54" t="n">
-        <v>7113050</v>
+        <v>7113578</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6099,12 +6099,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6118,7 +6118,7 @@
         <v>126863287</v>
       </c>
       <c r="B55" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>126867837</v>
       </c>
       <c r="B56" t="n">
-        <v>105381</v>
+        <v>105456</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>126864684</v>
       </c>
       <c r="B57" t="n">
-        <v>78384</v>
+        <v>78415</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -1040,7 +1040,7 @@
         <v>126862626</v>
       </c>
       <c r="B5" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>126868059</v>
       </c>
       <c r="B6" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>126864688</v>
       </c>
       <c r="B7" t="n">
-        <v>82852</v>
+        <v>82855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>126862625</v>
       </c>
       <c r="B8" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>126862596</v>
       </c>
       <c r="B9" t="n">
-        <v>99080</v>
+        <v>99086</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,45 +1543,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126868057</v>
+        <v>126867857</v>
       </c>
       <c r="B10" t="n">
-        <v>91319</v>
+        <v>98442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>699944</v>
+        <v>699822</v>
       </c>
       <c r="R10" t="n">
-        <v>7113181</v>
+        <v>7113408</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,18 +1634,19 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1644,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126850606</v>
+        <v>126868057</v>
       </c>
       <c r="B11" t="n">
-        <v>57817</v>
+        <v>91325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,37 +1668,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nydala, Nydala, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>699845</v>
+        <v>699944</v>
       </c>
       <c r="R11" t="n">
-        <v>7113169</v>
+        <v>7113181</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1729,72 +1742,64 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Torbjörn Söderquist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126867857</v>
+        <v>126850606</v>
       </c>
       <c r="B12" t="n">
-        <v>98436</v>
+        <v>57817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Nydala, Nydala, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>699822</v>
+        <v>699845</v>
       </c>
       <c r="R12" t="n">
-        <v>7113408</v>
+        <v>7113169</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1832,7 +1837,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1847,18 +1851,14 @@
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>126868067</v>
       </c>
       <c r="B13" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,10 +1961,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126862664</v>
+        <v>126864681</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>80117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,21 +1972,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>699735</v>
+        <v>699880</v>
       </c>
       <c r="R14" t="n">
-        <v>7113552</v>
+        <v>7113259</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,12 +2046,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126864681</v>
+        <v>126862664</v>
       </c>
       <c r="B15" t="n">
-        <v>80114</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,21 +2073,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>699880</v>
+        <v>699735</v>
       </c>
       <c r="R15" t="n">
-        <v>7113259</v>
+        <v>7113552</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,12 +2147,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2166,7 +2166,7 @@
         <v>126862622</v>
       </c>
       <c r="B16" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,45 +2377,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126867850</v>
+        <v>126868062</v>
       </c>
       <c r="B18" t="n">
-        <v>98457</v>
+        <v>57817</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>699955</v>
+        <v>699845</v>
       </c>
       <c r="R18" t="n">
-        <v>7113130</v>
+        <v>7113187</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,12 +2462,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2478,10 +2478,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126867848</v>
+        <v>126867850</v>
       </c>
       <c r="B19" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>699755</v>
+        <v>699955</v>
       </c>
       <c r="R19" t="n">
-        <v>7113586</v>
+        <v>7113130</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,45 +2579,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126868062</v>
+        <v>126867848</v>
       </c>
       <c r="B20" t="n">
-        <v>57817</v>
+        <v>98463</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>699845</v>
+        <v>699755</v>
       </c>
       <c r="R20" t="n">
-        <v>7113187</v>
+        <v>7113586</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,12 +2664,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2680,10 +2680,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126863282</v>
+        <v>126862599</v>
       </c>
       <c r="B21" t="n">
-        <v>91319</v>
+        <v>80118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,21 +2691,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>699958</v>
+        <v>699778</v>
       </c>
       <c r="R21" t="n">
-        <v>7113052</v>
+        <v>7113628</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,12 +2765,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126862599</v>
+        <v>126864675</v>
       </c>
       <c r="B22" t="n">
-        <v>80115</v>
+        <v>96695</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2792,21 +2792,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>699778</v>
+        <v>699913</v>
       </c>
       <c r="R22" t="n">
-        <v>7113628</v>
+        <v>7113203</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,12 +2866,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2882,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126864675</v>
+        <v>126863282</v>
       </c>
       <c r="B23" t="n">
-        <v>96689</v>
+        <v>91325</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2893,21 +2893,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>699913</v>
+        <v>699958</v>
       </c>
       <c r="R23" t="n">
-        <v>7113203</v>
+        <v>7113052</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2967,12 +2967,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2986,7 +2986,7 @@
         <v>126862624</v>
       </c>
       <c r="B24" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>126868058</v>
       </c>
       <c r="B25" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>126862598</v>
       </c>
       <c r="B26" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>126862669</v>
       </c>
       <c r="B27" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>126867894</v>
       </c>
       <c r="B28" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>126862570</v>
       </c>
       <c r="B29" t="n">
-        <v>105456</v>
+        <v>105462</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>126862627</v>
       </c>
       <c r="B30" t="n">
-        <v>80150</v>
+        <v>80153</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3690,10 +3690,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126864689</v>
+        <v>126867883</v>
       </c>
       <c r="B31" t="n">
-        <v>82852</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3701,34 +3701,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699933</v>
+        <v>699804</v>
       </c>
       <c r="R31" t="n">
-        <v>7113088</v>
+        <v>7113653</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3769,19 +3769,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3792,10 +3791,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126867883</v>
+        <v>126864689</v>
       </c>
       <c r="B32" t="n">
-        <v>79011</v>
+        <v>82855</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3803,34 +3802,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699804</v>
+        <v>699933</v>
       </c>
       <c r="R32" t="n">
-        <v>7113653</v>
+        <v>7113088</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3871,18 +3870,19 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3896,7 +3896,7 @@
         <v>126863288</v>
       </c>
       <c r="B33" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>126867886</v>
       </c>
       <c r="B34" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4095,10 +4095,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126862623</v>
+        <v>126863291</v>
       </c>
       <c r="B35" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699773</v>
+        <v>699885</v>
       </c>
       <c r="R35" t="n">
-        <v>7113587</v>
+        <v>7113259</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4180,12 +4180,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4297,10 +4297,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126863291</v>
+        <v>126862623</v>
       </c>
       <c r="B37" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699885</v>
+        <v>699773</v>
       </c>
       <c r="R37" t="n">
-        <v>7113259</v>
+        <v>7113587</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,12 +4382,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4398,27 +4398,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126867889</v>
+        <v>126862672</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>80152</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4429,14 +4429,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699818</v>
+        <v>699843</v>
       </c>
       <c r="R38" t="n">
-        <v>7113415</v>
+        <v>7113335</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4483,12 +4483,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4499,10 +4499,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126862672</v>
+        <v>126868055</v>
       </c>
       <c r="B39" t="n">
-        <v>80149</v>
+        <v>91290</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699843</v>
+        <v>699981</v>
       </c>
       <c r="R39" t="n">
-        <v>7113335</v>
+        <v>7113021</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4600,45 +4600,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126868055</v>
+        <v>126867889</v>
       </c>
       <c r="B40" t="n">
-        <v>91284</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699981</v>
+        <v>699818</v>
       </c>
       <c r="R40" t="n">
-        <v>7113021</v>
+        <v>7113415</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4685,12 +4685,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4704,7 +4704,7 @@
         <v>126867887</v>
       </c>
       <c r="B41" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>126862595</v>
       </c>
       <c r="B42" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4903,10 +4903,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126867884</v>
+        <v>126862628</v>
       </c>
       <c r="B43" t="n">
-        <v>79011</v>
+        <v>80117</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4914,34 +4914,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699877</v>
+        <v>699783</v>
       </c>
       <c r="R43" t="n">
-        <v>7113569</v>
+        <v>7113533</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4988,12 +4988,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5004,10 +5004,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126862628</v>
+        <v>126867884</v>
       </c>
       <c r="B44" t="n">
-        <v>80114</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5015,34 +5015,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699783</v>
+        <v>699877</v>
       </c>
       <c r="R44" t="n">
-        <v>7113533</v>
+        <v>7113569</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5089,12 +5089,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5108,7 +5108,7 @@
         <v>126862671</v>
       </c>
       <c r="B45" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5206,32 +5206,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126862620</v>
+        <v>126862659</v>
       </c>
       <c r="B46" t="n">
-        <v>80114</v>
+        <v>75121</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5241,10 +5241,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699885</v>
+        <v>699845</v>
       </c>
       <c r="R46" t="n">
-        <v>7113266</v>
+        <v>7113325</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5307,45 +5307,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126867851</v>
+        <v>126862620</v>
       </c>
       <c r="B47" t="n">
-        <v>98457</v>
+        <v>80117</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699963</v>
+        <v>699885</v>
       </c>
       <c r="R47" t="n">
-        <v>7113120</v>
+        <v>7113266</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,12 +5392,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5411,7 +5411,7 @@
         <v>126862581</v>
       </c>
       <c r="B48" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126862659</v>
+        <v>126867851</v>
       </c>
       <c r="B49" t="n">
-        <v>75118</v>
+        <v>98463</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5520,34 +5520,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6439</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>699845</v>
+        <v>699963</v>
       </c>
       <c r="R49" t="n">
-        <v>7113325</v>
+        <v>7113120</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5594,12 +5594,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5613,7 +5613,7 @@
         <v>126864677</v>
       </c>
       <c r="B50" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>126867890</v>
       </c>
       <c r="B51" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>126864676</v>
       </c>
       <c r="B52" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5913,10 +5913,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126863289</v>
+        <v>126862568</v>
       </c>
       <c r="B53" t="n">
-        <v>97314</v>
+        <v>105462</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5924,21 +5924,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>699799</v>
+        <v>699772</v>
       </c>
       <c r="R53" t="n">
-        <v>7113391</v>
+        <v>7113578</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5998,12 +5998,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6014,10 +6014,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126862568</v>
+        <v>126863289</v>
       </c>
       <c r="B54" t="n">
-        <v>105456</v>
+        <v>97320</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6025,21 +6025,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6049,10 +6049,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>699772</v>
+        <v>699799</v>
       </c>
       <c r="R54" t="n">
-        <v>7113578</v>
+        <v>7113391</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6099,12 +6099,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6118,7 +6118,7 @@
         <v>126863287</v>
       </c>
       <c r="B55" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>126867837</v>
       </c>
       <c r="B56" t="n">
-        <v>105456</v>
+        <v>105462</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>126864684</v>
       </c>
       <c r="B57" t="n">
-        <v>78415</v>
+        <v>78418</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126862626</v>
+        <v>126864688</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>82855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699893</v>
+        <v>699884</v>
       </c>
       <c r="R5" t="n">
-        <v>7113185</v>
+        <v>7113179</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,18 +1116,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1239,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126864688</v>
+        <v>126862626</v>
       </c>
       <c r="B7" t="n">
-        <v>82855</v>
+        <v>80117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1274,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>699884</v>
+        <v>699893</v>
       </c>
       <c r="R7" t="n">
-        <v>7113179</v>
+        <v>7113185</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,19 +1319,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1341,32 +1341,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126862625</v>
+        <v>126862596</v>
       </c>
       <c r="B8" t="n">
-        <v>80117</v>
+        <v>99086</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>222302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>699832</v>
+        <v>699829</v>
       </c>
       <c r="R8" t="n">
-        <v>7113407</v>
+        <v>7113383</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1442,32 +1442,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126862596</v>
+        <v>126862625</v>
       </c>
       <c r="B9" t="n">
-        <v>99086</v>
+        <v>80117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222302</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>699829</v>
+        <v>699832</v>
       </c>
       <c r="R9" t="n">
-        <v>7113383</v>
+        <v>7113407</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1543,57 +1543,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126867857</v>
+        <v>126868057</v>
       </c>
       <c r="B10" t="n">
-        <v>98442</v>
+        <v>91325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>699822</v>
+        <v>699944</v>
       </c>
       <c r="R10" t="n">
-        <v>7113408</v>
+        <v>7113181</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,19 +1622,18 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1657,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126868057</v>
+        <v>126850606</v>
       </c>
       <c r="B11" t="n">
-        <v>91325</v>
+        <v>57817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,37 +1655,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Nydala, Nydala, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>699944</v>
+        <v>699845</v>
       </c>
       <c r="R11" t="n">
-        <v>7113181</v>
+        <v>7113169</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1742,64 +1729,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126850606</v>
+        <v>126868067</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>98359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nydala, Nydala, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>699845</v>
+        <v>699947</v>
       </c>
       <c r="R12" t="n">
-        <v>7113169</v>
+        <v>7113090</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1829,6 +1812,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 20 st på liten yta</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,57 +1831,73 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Torbjörn Söderquist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126868067</v>
+        <v>126867857</v>
       </c>
       <c r="B13" t="n">
-        <v>98359</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>699947</v>
+        <v>699822</v>
       </c>
       <c r="R13" t="n">
-        <v>7113090</v>
+        <v>7113408</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,29 +1932,25 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ca 20 st på liten yta</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1961,10 +1961,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126864681</v>
+        <v>126862664</v>
       </c>
       <c r="B14" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,21 +1972,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>699880</v>
+        <v>699735</v>
       </c>
       <c r="R14" t="n">
-        <v>7113259</v>
+        <v>7113552</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,12 +2046,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126862664</v>
+        <v>126864681</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,21 +2073,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>699735</v>
+        <v>699880</v>
       </c>
       <c r="R15" t="n">
-        <v>7113552</v>
+        <v>7113259</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,12 +2147,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2680,10 +2680,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126862599</v>
+        <v>126864675</v>
       </c>
       <c r="B21" t="n">
-        <v>80118</v>
+        <v>96695</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,21 +2691,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>699778</v>
+        <v>699913</v>
       </c>
       <c r="R21" t="n">
-        <v>7113628</v>
+        <v>7113203</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,12 +2765,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126864675</v>
+        <v>126863282</v>
       </c>
       <c r="B22" t="n">
-        <v>96695</v>
+        <v>91325</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2792,21 +2792,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>699913</v>
+        <v>699958</v>
       </c>
       <c r="R22" t="n">
-        <v>7113203</v>
+        <v>7113052</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,12 +2866,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2882,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126863282</v>
+        <v>126862599</v>
       </c>
       <c r="B23" t="n">
-        <v>91325</v>
+        <v>80118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2893,21 +2893,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>699958</v>
+        <v>699778</v>
       </c>
       <c r="R23" t="n">
-        <v>7113052</v>
+        <v>7113628</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2967,12 +2967,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3286,10 +3286,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126862669</v>
+        <v>126862570</v>
       </c>
       <c r="B27" t="n">
-        <v>98359</v>
+        <v>105462</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3297,21 +3297,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>221725</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699879</v>
+        <v>699830</v>
       </c>
       <c r="R27" t="n">
-        <v>7113265</v>
+        <v>7113371</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,7 +3387,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126867894</v>
+        <v>126862669</v>
       </c>
       <c r="B28" t="n">
         <v>98359</v>
@@ -3418,14 +3418,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699948</v>
+        <v>699879</v>
       </c>
       <c r="R28" t="n">
-        <v>7113110</v>
+        <v>7113265</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,12 +3472,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3488,10 +3488,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126862570</v>
+        <v>126867894</v>
       </c>
       <c r="B29" t="n">
-        <v>105462</v>
+        <v>98359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221725</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699830</v>
+        <v>699948</v>
       </c>
       <c r="R29" t="n">
-        <v>7113371</v>
+        <v>7113110</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3573,12 +3573,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3690,10 +3690,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126867883</v>
+        <v>126864689</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>82855</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3701,34 +3701,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699804</v>
+        <v>699933</v>
       </c>
       <c r="R31" t="n">
-        <v>7113653</v>
+        <v>7113088</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3769,18 +3769,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3791,10 +3792,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126864689</v>
+        <v>126867883</v>
       </c>
       <c r="B32" t="n">
-        <v>82855</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3802,34 +3803,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699933</v>
+        <v>699804</v>
       </c>
       <c r="R32" t="n">
-        <v>7113088</v>
+        <v>7113653</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,19 +3871,18 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4095,7 +4095,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126863291</v>
+        <v>126862623</v>
       </c>
       <c r="B35" t="n">
         <v>80117</v>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699885</v>
+        <v>699773</v>
       </c>
       <c r="R35" t="n">
-        <v>7113259</v>
+        <v>7113587</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4180,12 +4180,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4196,10 +4196,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126867844</v>
+        <v>126863291</v>
       </c>
       <c r="B36" t="n">
-        <v>57817</v>
+        <v>80117</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4207,34 +4207,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699887</v>
+        <v>699885</v>
       </c>
       <c r="R36" t="n">
-        <v>7113380</v>
+        <v>7113259</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4281,12 +4281,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4297,10 +4297,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126862623</v>
+        <v>126867844</v>
       </c>
       <c r="B37" t="n">
-        <v>80117</v>
+        <v>57817</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4308,34 +4308,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699773</v>
+        <v>699887</v>
       </c>
       <c r="R37" t="n">
-        <v>7113587</v>
+        <v>7113380</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,12 +4382,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4398,10 +4398,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126862672</v>
+        <v>126868055</v>
       </c>
       <c r="B38" t="n">
-        <v>80152</v>
+        <v>91290</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699843</v>
+        <v>699981</v>
       </c>
       <c r="R38" t="n">
-        <v>7113335</v>
+        <v>7113021</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4483,12 +4483,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4499,10 +4499,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126868055</v>
+        <v>126862672</v>
       </c>
       <c r="B39" t="n">
-        <v>91290</v>
+        <v>80152</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699981</v>
+        <v>699843</v>
       </c>
       <c r="R39" t="n">
-        <v>7113021</v>
+        <v>7113335</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4802,32 +4802,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126862595</v>
+        <v>126862628</v>
       </c>
       <c r="B42" t="n">
-        <v>80146</v>
+        <v>80117</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699848</v>
+        <v>699783</v>
       </c>
       <c r="R42" t="n">
-        <v>7113330</v>
+        <v>7113533</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4903,32 +4903,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126862628</v>
+        <v>126862671</v>
       </c>
       <c r="B43" t="n">
-        <v>80117</v>
+        <v>98359</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699783</v>
+        <v>699946</v>
       </c>
       <c r="R43" t="n">
-        <v>7113533</v>
+        <v>7113098</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5105,10 +5105,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126862671</v>
+        <v>126862595</v>
       </c>
       <c r="B45" t="n">
-        <v>98359</v>
+        <v>80146</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5116,21 +5116,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699946</v>
+        <v>699848</v>
       </c>
       <c r="R45" t="n">
-        <v>7113098</v>
+        <v>7113330</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5408,10 +5408,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126862581</v>
+        <v>126867851</v>
       </c>
       <c r="B48" t="n">
-        <v>91290</v>
+        <v>98463</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5419,34 +5419,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>699816</v>
+        <v>699963</v>
       </c>
       <c r="R48" t="n">
-        <v>7113390</v>
+        <v>7113120</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5493,12 +5493,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5509,10 +5509,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126867851</v>
+        <v>126862581</v>
       </c>
       <c r="B49" t="n">
-        <v>98463</v>
+        <v>91290</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5520,34 +5520,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>699963</v>
+        <v>699816</v>
       </c>
       <c r="R49" t="n">
-        <v>7113120</v>
+        <v>7113390</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5594,12 +5594,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5711,45 +5711,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126867890</v>
+        <v>126864676</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>91290</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>699832</v>
+        <v>699986</v>
       </c>
       <c r="R51" t="n">
-        <v>7113381</v>
+        <v>7113023</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5796,12 +5796,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5812,10 +5812,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126864676</v>
+        <v>126862568</v>
       </c>
       <c r="B52" t="n">
-        <v>91290</v>
+        <v>105462</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5823,21 +5823,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>699986</v>
+        <v>699772</v>
       </c>
       <c r="R52" t="n">
-        <v>7113023</v>
+        <v>7113578</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,12 +5897,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5913,45 +5913,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126862568</v>
+        <v>126867890</v>
       </c>
       <c r="B53" t="n">
-        <v>105462</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>699772</v>
+        <v>699832</v>
       </c>
       <c r="R53" t="n">
-        <v>7113578</v>
+        <v>7113381</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5998,12 +5998,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126864688</v>
+        <v>126862626</v>
       </c>
       <c r="B5" t="n">
-        <v>82855</v>
+        <v>80117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699884</v>
+        <v>699893</v>
       </c>
       <c r="R5" t="n">
-        <v>7113179</v>
+        <v>7113185</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,19 +1116,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1139,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126868059</v>
+        <v>126864688</v>
       </c>
       <c r="B6" t="n">
-        <v>91325</v>
+        <v>82855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699956</v>
+        <v>699884</v>
       </c>
       <c r="R6" t="n">
-        <v>7113052</v>
+        <v>7113179</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,18 +1217,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126862626</v>
+        <v>126868059</v>
       </c>
       <c r="B7" t="n">
-        <v>80117</v>
+        <v>91325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>699893</v>
+        <v>699956</v>
       </c>
       <c r="R7" t="n">
-        <v>7113185</v>
+        <v>7113052</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,12 +1325,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126864688</v>
+        <v>126868059</v>
       </c>
       <c r="B6" t="n">
-        <v>82855</v>
+        <v>91326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699884</v>
+        <v>699956</v>
       </c>
       <c r="R6" t="n">
-        <v>7113179</v>
+        <v>7113052</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,19 +1217,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1240,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126868059</v>
+        <v>126864688</v>
       </c>
       <c r="B7" t="n">
-        <v>91325</v>
+        <v>82855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1250,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>699956</v>
+        <v>699884</v>
       </c>
       <c r="R7" t="n">
-        <v>7113052</v>
+        <v>7113179</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,18 +1318,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1344,7 +1344,7 @@
         <v>126862596</v>
       </c>
       <c r="B8" t="n">
-        <v>99086</v>
+        <v>99087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1543,32 +1543,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126868057</v>
+        <v>126868067</v>
       </c>
       <c r="B10" t="n">
-        <v>91325</v>
+        <v>98360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>699944</v>
+        <v>699947</v>
       </c>
       <c r="R10" t="n">
-        <v>7113181</v>
+        <v>7113090</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,6 +1614,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca 20 st på liten yta</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,48 +1649,60 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126850606</v>
+        <v>126867857</v>
       </c>
       <c r="B11" t="n">
-        <v>57817</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nydala, Nydala, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>699845</v>
+        <v>699822</v>
       </c>
       <c r="R11" t="n">
-        <v>7113169</v>
+        <v>7113408</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1723,6 +1740,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1737,36 +1755,40 @@
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126868067</v>
+        <v>126868057</v>
       </c>
       <c r="B12" t="n">
-        <v>98359</v>
+        <v>91326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>699947</v>
+        <v>699944</v>
       </c>
       <c r="R12" t="n">
-        <v>7113090</v>
+        <v>7113181</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,11 +1834,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 20 st på liten yta</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,60 +1864,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126867857</v>
+        <v>126850606</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>57817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Nydala, Nydala, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>699822</v>
+        <v>699845</v>
       </c>
       <c r="R13" t="n">
-        <v>7113408</v>
+        <v>7113169</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1938,7 +1943,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1953,11 +1957,7 @@
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2481,7 +2481,7 @@
         <v>126867850</v>
       </c>
       <c r="B19" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>126867848</v>
       </c>
       <c r="B20" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,10 +2680,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126864675</v>
+        <v>126862624</v>
       </c>
       <c r="B21" t="n">
-        <v>96695</v>
+        <v>80117</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,21 +2691,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>699913</v>
+        <v>699857</v>
       </c>
       <c r="R21" t="n">
-        <v>7113203</v>
+        <v>7113431</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,12 +2765,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126863282</v>
+        <v>126862599</v>
       </c>
       <c r="B22" t="n">
-        <v>91325</v>
+        <v>80118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2792,21 +2792,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>699958</v>
+        <v>699778</v>
       </c>
       <c r="R22" t="n">
-        <v>7113052</v>
+        <v>7113628</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,12 +2866,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2882,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126862599</v>
+        <v>126863282</v>
       </c>
       <c r="B23" t="n">
-        <v>80118</v>
+        <v>91326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2893,21 +2893,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>699778</v>
+        <v>699958</v>
       </c>
       <c r="R23" t="n">
-        <v>7113628</v>
+        <v>7113052</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2967,12 +2967,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2983,10 +2983,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126862624</v>
+        <v>126864675</v>
       </c>
       <c r="B24" t="n">
-        <v>80117</v>
+        <v>96696</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2994,21 +2994,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>699857</v>
+        <v>699913</v>
       </c>
       <c r="R24" t="n">
-        <v>7113431</v>
+        <v>7113203</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3068,12 +3068,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3084,32 +3084,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126868058</v>
+        <v>126862598</v>
       </c>
       <c r="B25" t="n">
-        <v>91325</v>
+        <v>98464</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699940</v>
+        <v>699820</v>
       </c>
       <c r="R25" t="n">
-        <v>7113194</v>
+        <v>7113394</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3169,12 +3169,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3185,32 +3185,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126862598</v>
+        <v>126868058</v>
       </c>
       <c r="B26" t="n">
-        <v>98463</v>
+        <v>91326</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699820</v>
+        <v>699940</v>
       </c>
       <c r="R26" t="n">
-        <v>7113394</v>
+        <v>7113194</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3270,12 +3270,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3286,10 +3286,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126862570</v>
+        <v>126862627</v>
       </c>
       <c r="B27" t="n">
-        <v>105462</v>
+        <v>80153</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3297,21 +3297,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221725</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699830</v>
+        <v>699788</v>
       </c>
       <c r="R27" t="n">
-        <v>7113371</v>
+        <v>7113541</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3387,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126862669</v>
+        <v>126862570</v>
       </c>
       <c r="B28" t="n">
-        <v>98359</v>
+        <v>105463</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,21 +3398,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>221725</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699879</v>
+        <v>699830</v>
       </c>
       <c r="R28" t="n">
-        <v>7113265</v>
+        <v>7113371</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3488,10 +3488,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126867894</v>
+        <v>126862669</v>
       </c>
       <c r="B29" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3519,14 +3519,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699948</v>
+        <v>699879</v>
       </c>
       <c r="R29" t="n">
-        <v>7113110</v>
+        <v>7113265</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3573,12 +3573,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126862627</v>
+        <v>126867894</v>
       </c>
       <c r="B30" t="n">
-        <v>80153</v>
+        <v>98360</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3600,34 +3600,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699788</v>
+        <v>699948</v>
       </c>
       <c r="R30" t="n">
-        <v>7113541</v>
+        <v>7113110</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3674,12 +3674,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3690,10 +3690,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126864689</v>
+        <v>126867883</v>
       </c>
       <c r="B31" t="n">
-        <v>82855</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3701,34 +3701,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699933</v>
+        <v>699804</v>
       </c>
       <c r="R31" t="n">
-        <v>7113088</v>
+        <v>7113653</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3769,19 +3769,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3792,10 +3791,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126867883</v>
+        <v>126864689</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>82855</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3803,34 +3802,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699804</v>
+        <v>699933</v>
       </c>
       <c r="R32" t="n">
-        <v>7113653</v>
+        <v>7113088</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3871,18 +3870,19 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3896,7 +3896,7 @@
         <v>126863288</v>
       </c>
       <c r="B33" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4095,10 +4095,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126862623</v>
+        <v>126867844</v>
       </c>
       <c r="B35" t="n">
-        <v>80117</v>
+        <v>57817</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4106,34 +4106,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699773</v>
+        <v>699887</v>
       </c>
       <c r="R35" t="n">
-        <v>7113587</v>
+        <v>7113380</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4180,12 +4180,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4196,7 +4196,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126863291</v>
+        <v>126862623</v>
       </c>
       <c r="B36" t="n">
         <v>80117</v>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699885</v>
+        <v>699773</v>
       </c>
       <c r="R36" t="n">
-        <v>7113259</v>
+        <v>7113587</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4281,12 +4281,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4297,10 +4297,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126867844</v>
+        <v>126863291</v>
       </c>
       <c r="B37" t="n">
-        <v>57817</v>
+        <v>80117</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4308,34 +4308,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699887</v>
+        <v>699885</v>
       </c>
       <c r="R37" t="n">
-        <v>7113380</v>
+        <v>7113259</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,12 +4382,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4401,7 +4401,7 @@
         <v>126868055</v>
       </c>
       <c r="B38" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4499,27 +4499,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126862672</v>
+        <v>126867889</v>
       </c>
       <c r="B39" t="n">
-        <v>80152</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4530,14 +4530,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699843</v>
+        <v>699818</v>
       </c>
       <c r="R39" t="n">
-        <v>7113335</v>
+        <v>7113415</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4600,27 +4600,27 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126867889</v>
+        <v>126862672</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>80152</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4631,14 +4631,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699818</v>
+        <v>699843</v>
       </c>
       <c r="R40" t="n">
-        <v>7113415</v>
+        <v>7113335</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4685,12 +4685,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4802,32 +4802,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126862628</v>
+        <v>126862595</v>
       </c>
       <c r="B42" t="n">
-        <v>80117</v>
+        <v>80146</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699783</v>
+        <v>699848</v>
       </c>
       <c r="R42" t="n">
-        <v>7113533</v>
+        <v>7113330</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4903,32 +4903,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126862671</v>
+        <v>126862628</v>
       </c>
       <c r="B43" t="n">
-        <v>98359</v>
+        <v>80117</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699946</v>
+        <v>699783</v>
       </c>
       <c r="R43" t="n">
-        <v>7113098</v>
+        <v>7113533</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5105,10 +5105,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126862595</v>
+        <v>126862671</v>
       </c>
       <c r="B45" t="n">
-        <v>80146</v>
+        <v>98360</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5116,21 +5116,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699848</v>
+        <v>699946</v>
       </c>
       <c r="R45" t="n">
-        <v>7113330</v>
+        <v>7113098</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5206,10 +5206,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126862659</v>
+        <v>126867851</v>
       </c>
       <c r="B46" t="n">
-        <v>75121</v>
+        <v>98464</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5217,34 +5217,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6439</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699845</v>
+        <v>699963</v>
       </c>
       <c r="R46" t="n">
-        <v>7113325</v>
+        <v>7113120</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5291,12 +5291,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5307,32 +5307,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126862620</v>
+        <v>126862581</v>
       </c>
       <c r="B47" t="n">
-        <v>80117</v>
+        <v>91291</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699885</v>
+        <v>699816</v>
       </c>
       <c r="R47" t="n">
-        <v>7113266</v>
+        <v>7113390</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5408,10 +5408,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126867851</v>
+        <v>126862659</v>
       </c>
       <c r="B48" t="n">
-        <v>98463</v>
+        <v>75121</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5419,34 +5419,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>6439</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>699963</v>
+        <v>699845</v>
       </c>
       <c r="R48" t="n">
-        <v>7113120</v>
+        <v>7113325</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5493,12 +5493,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5509,32 +5509,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126862581</v>
+        <v>126862620</v>
       </c>
       <c r="B49" t="n">
-        <v>91290</v>
+        <v>80117</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>699816</v>
+        <v>699885</v>
       </c>
       <c r="R49" t="n">
-        <v>7113390</v>
+        <v>7113266</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5610,32 +5610,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126864677</v>
+        <v>126864676</v>
       </c>
       <c r="B50" t="n">
-        <v>91325</v>
+        <v>91291</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>699961</v>
+        <v>699986</v>
       </c>
       <c r="R50" t="n">
-        <v>7113050</v>
+        <v>7113023</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5711,45 +5711,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126864676</v>
+        <v>126867890</v>
       </c>
       <c r="B51" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>699986</v>
+        <v>699832</v>
       </c>
       <c r="R51" t="n">
-        <v>7113023</v>
+        <v>7113381</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5796,12 +5796,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5812,32 +5812,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126862568</v>
+        <v>126864677</v>
       </c>
       <c r="B52" t="n">
-        <v>105462</v>
+        <v>91326</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>699772</v>
+        <v>699961</v>
       </c>
       <c r="R52" t="n">
-        <v>7113578</v>
+        <v>7113050</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,12 +5897,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5913,45 +5913,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126867890</v>
+        <v>126862568</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>105463</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>699832</v>
+        <v>699772</v>
       </c>
       <c r="R53" t="n">
-        <v>7113381</v>
+        <v>7113578</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5998,12 +5998,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6017,7 +6017,7 @@
         <v>126863289</v>
       </c>
       <c r="B54" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>126863287</v>
       </c>
       <c r="B55" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>126867837</v>
       </c>
       <c r="B56" t="n">
-        <v>105462</v>
+        <v>105463</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -1543,48 +1543,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126868067</v>
+        <v>126850606</v>
       </c>
       <c r="B10" t="n">
-        <v>98360</v>
+        <v>57817</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Nydala, Nydala, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>699947</v>
+        <v>699845</v>
       </c>
       <c r="R10" t="n">
-        <v>7113090</v>
+        <v>7113169</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1614,11 +1614,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ca 20 st på liten yta</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,19 +1628,15 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1864,48 +1855,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126850606</v>
+        <v>126868067</v>
       </c>
       <c r="B13" t="n">
-        <v>57817</v>
+        <v>98360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nydala, Nydala, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>699845</v>
+        <v>699947</v>
       </c>
       <c r="R13" t="n">
-        <v>7113169</v>
+        <v>7113090</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1935,6 +1926,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ca 20 st på liten yta</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,15 +1945,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Torbjörn Söderquist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2377,45 +2377,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126868062</v>
+        <v>126867850</v>
       </c>
       <c r="B18" t="n">
-        <v>57817</v>
+        <v>98464</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>699845</v>
+        <v>699955</v>
       </c>
       <c r="R18" t="n">
-        <v>7113187</v>
+        <v>7113130</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,12 +2462,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2478,7 +2478,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126867850</v>
+        <v>126867848</v>
       </c>
       <c r="B19" t="n">
         <v>98464</v>
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>699955</v>
+        <v>699755</v>
       </c>
       <c r="R19" t="n">
-        <v>7113130</v>
+        <v>7113586</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,45 +2579,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126867848</v>
+        <v>126868062</v>
       </c>
       <c r="B20" t="n">
-        <v>98464</v>
+        <v>57817</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>699755</v>
+        <v>699845</v>
       </c>
       <c r="R20" t="n">
-        <v>7113586</v>
+        <v>7113187</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,12 +2664,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2680,10 +2680,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126862624</v>
+        <v>126862599</v>
       </c>
       <c r="B21" t="n">
-        <v>80117</v>
+        <v>80118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,21 +2691,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>699857</v>
+        <v>699778</v>
       </c>
       <c r="R21" t="n">
-        <v>7113431</v>
+        <v>7113628</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126862599</v>
+        <v>126862624</v>
       </c>
       <c r="B22" t="n">
-        <v>80118</v>
+        <v>80117</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2792,21 +2792,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>699778</v>
+        <v>699857</v>
       </c>
       <c r="R22" t="n">
-        <v>7113628</v>
+        <v>7113431</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -5004,45 +5004,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126867884</v>
+        <v>126862671</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699877</v>
+        <v>699946</v>
       </c>
       <c r="R44" t="n">
-        <v>7113569</v>
+        <v>7113098</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5089,12 +5089,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5105,45 +5105,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126862671</v>
+        <v>126867884</v>
       </c>
       <c r="B45" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699946</v>
+        <v>699877</v>
       </c>
       <c r="R45" t="n">
-        <v>7113098</v>
+        <v>7113569</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5190,12 +5190,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5307,10 +5307,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126862581</v>
+        <v>126862659</v>
       </c>
       <c r="B47" t="n">
-        <v>91291</v>
+        <v>75121</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,21 +5318,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>6439</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699816</v>
+        <v>699845</v>
       </c>
       <c r="R47" t="n">
-        <v>7113390</v>
+        <v>7113325</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5408,32 +5408,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126862659</v>
+        <v>126862620</v>
       </c>
       <c r="B48" t="n">
-        <v>75121</v>
+        <v>80117</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>699845</v>
+        <v>699885</v>
       </c>
       <c r="R48" t="n">
-        <v>7113325</v>
+        <v>7113266</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5509,32 +5509,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126862620</v>
+        <v>126862581</v>
       </c>
       <c r="B49" t="n">
-        <v>80117</v>
+        <v>91291</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>699885</v>
+        <v>699816</v>
       </c>
       <c r="R49" t="n">
-        <v>7113266</v>
+        <v>7113390</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126862626</v>
+        <v>126868059</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>91326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699893</v>
+        <v>699956</v>
       </c>
       <c r="R5" t="n">
-        <v>7113185</v>
+        <v>7113052</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,12 +1122,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126868059</v>
+        <v>126864688</v>
       </c>
       <c r="B6" t="n">
-        <v>91326</v>
+        <v>82855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699956</v>
+        <v>699884</v>
       </c>
       <c r="R6" t="n">
-        <v>7113052</v>
+        <v>7113179</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,18 +1217,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1239,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126864688</v>
+        <v>126862626</v>
       </c>
       <c r="B7" t="n">
-        <v>82855</v>
+        <v>80117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1274,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>699884</v>
+        <v>699893</v>
       </c>
       <c r="R7" t="n">
-        <v>7113179</v>
+        <v>7113185</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,19 +1319,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1341,32 +1341,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126862596</v>
+        <v>126862625</v>
       </c>
       <c r="B8" t="n">
-        <v>99087</v>
+        <v>80117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222302</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>699829</v>
+        <v>699832</v>
       </c>
       <c r="R8" t="n">
-        <v>7113383</v>
+        <v>7113407</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,32 +1442,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126862625</v>
+        <v>126862596</v>
       </c>
       <c r="B9" t="n">
-        <v>80117</v>
+        <v>99087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>222302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>699832</v>
+        <v>699829</v>
       </c>
       <c r="R9" t="n">
-        <v>7113407</v>
+        <v>7113383</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126850606</v>
+        <v>126868057</v>
       </c>
       <c r="B10" t="n">
-        <v>57817</v>
+        <v>91326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,37 +1554,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nydala, Nydala, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>699845</v>
+        <v>699944</v>
       </c>
       <c r="R10" t="n">
-        <v>7113169</v>
+        <v>7113181</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,72 +1628,64 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Torbjörn Söderquist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126867857</v>
+        <v>126850606</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>57817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Nydala, Nydala, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>699822</v>
+        <v>699845</v>
       </c>
       <c r="R11" t="n">
-        <v>7113408</v>
+        <v>7113169</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1731,7 +1723,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1746,53 +1737,61 @@
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126868057</v>
+        <v>126867857</v>
       </c>
       <c r="B12" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>699944</v>
+        <v>699822</v>
       </c>
       <c r="R12" t="n">
-        <v>7113181</v>
+        <v>7113408</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,18 +1832,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1961,10 +1961,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126862664</v>
+        <v>126864681</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,21 +1972,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>699735</v>
+        <v>699880</v>
       </c>
       <c r="R14" t="n">
-        <v>7113552</v>
+        <v>7113259</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,12 +2046,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson, Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126864681</v>
+        <v>126862664</v>
       </c>
       <c r="B15" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,21 +2073,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>699880</v>
+        <v>699735</v>
       </c>
       <c r="R15" t="n">
-        <v>7113259</v>
+        <v>7113552</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,12 +2147,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2680,10 +2680,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126862599</v>
+        <v>126864675</v>
       </c>
       <c r="B21" t="n">
-        <v>80118</v>
+        <v>96696</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,21 +2691,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>699778</v>
+        <v>699913</v>
       </c>
       <c r="R21" t="n">
-        <v>7113628</v>
+        <v>7113203</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,12 +2765,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2983,10 +2983,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126864675</v>
+        <v>126862599</v>
       </c>
       <c r="B24" t="n">
-        <v>96696</v>
+        <v>80118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2994,21 +2994,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>699913</v>
+        <v>699778</v>
       </c>
       <c r="R24" t="n">
-        <v>7113203</v>
+        <v>7113628</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3068,12 +3068,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3084,32 +3084,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126862598</v>
+        <v>126868058</v>
       </c>
       <c r="B25" t="n">
-        <v>98464</v>
+        <v>91326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699820</v>
+        <v>699940</v>
       </c>
       <c r="R25" t="n">
-        <v>7113394</v>
+        <v>7113194</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3169,12 +3169,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3185,32 +3185,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126868058</v>
+        <v>126862598</v>
       </c>
       <c r="B26" t="n">
-        <v>91326</v>
+        <v>98464</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699940</v>
+        <v>699820</v>
       </c>
       <c r="R26" t="n">
-        <v>7113194</v>
+        <v>7113394</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3270,12 +3270,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3690,10 +3690,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126867883</v>
+        <v>126864689</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>82855</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3701,34 +3701,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699804</v>
+        <v>699933</v>
       </c>
       <c r="R31" t="n">
-        <v>7113653</v>
+        <v>7113088</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3769,18 +3769,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3791,10 +3792,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126864689</v>
+        <v>126867883</v>
       </c>
       <c r="B32" t="n">
-        <v>82855</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3802,34 +3803,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699933</v>
+        <v>699804</v>
       </c>
       <c r="R32" t="n">
-        <v>7113088</v>
+        <v>7113653</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,19 +3871,18 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3893,10 +3893,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126863288</v>
+        <v>126867886</v>
       </c>
       <c r="B33" t="n">
-        <v>91622</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3904,34 +3904,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699939</v>
+        <v>699878</v>
       </c>
       <c r="R33" t="n">
-        <v>7113199</v>
+        <v>7113551</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3978,12 +3978,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3994,10 +3994,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126867886</v>
+        <v>126863288</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>91622</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4005,34 +4005,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699878</v>
+        <v>699939</v>
       </c>
       <c r="R34" t="n">
-        <v>7113551</v>
+        <v>7113199</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4079,12 +4079,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4095,10 +4095,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126867844</v>
+        <v>126862623</v>
       </c>
       <c r="B35" t="n">
-        <v>57817</v>
+        <v>80117</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4106,34 +4106,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699887</v>
+        <v>699773</v>
       </c>
       <c r="R35" t="n">
-        <v>7113380</v>
+        <v>7113587</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4180,12 +4180,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4196,7 +4196,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126862623</v>
+        <v>126863291</v>
       </c>
       <c r="B36" t="n">
         <v>80117</v>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699773</v>
+        <v>699885</v>
       </c>
       <c r="R36" t="n">
-        <v>7113587</v>
+        <v>7113259</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4281,12 +4281,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4297,10 +4297,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126863291</v>
+        <v>126867844</v>
       </c>
       <c r="B37" t="n">
-        <v>80117</v>
+        <v>57817</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4308,34 +4308,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699885</v>
+        <v>699887</v>
       </c>
       <c r="R37" t="n">
-        <v>7113259</v>
+        <v>7113380</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,12 +4382,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4499,27 +4499,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126867889</v>
+        <v>126862672</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>80152</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4530,14 +4530,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699818</v>
+        <v>699843</v>
       </c>
       <c r="R39" t="n">
-        <v>7113415</v>
+        <v>7113335</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4600,27 +4600,27 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126862672</v>
+        <v>126867889</v>
       </c>
       <c r="B40" t="n">
-        <v>80152</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4631,14 +4631,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699843</v>
+        <v>699818</v>
       </c>
       <c r="R40" t="n">
-        <v>7113335</v>
+        <v>7113415</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4685,12 +4685,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4802,32 +4802,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126862595</v>
+        <v>126862628</v>
       </c>
       <c r="B42" t="n">
-        <v>80146</v>
+        <v>80117</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699848</v>
+        <v>699783</v>
       </c>
       <c r="R42" t="n">
-        <v>7113330</v>
+        <v>7113533</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4903,10 +4903,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126862628</v>
+        <v>126867884</v>
       </c>
       <c r="B43" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4914,34 +4914,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699783</v>
+        <v>699877</v>
       </c>
       <c r="R43" t="n">
-        <v>7113533</v>
+        <v>7113569</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4988,12 +4988,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5004,10 +5004,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126862671</v>
+        <v>126862595</v>
       </c>
       <c r="B44" t="n">
-        <v>98360</v>
+        <v>80146</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5015,21 +5015,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699946</v>
+        <v>699848</v>
       </c>
       <c r="R44" t="n">
-        <v>7113098</v>
+        <v>7113330</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5105,45 +5105,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126867884</v>
+        <v>126862671</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699877</v>
+        <v>699946</v>
       </c>
       <c r="R45" t="n">
-        <v>7113569</v>
+        <v>7113098</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5190,12 +5190,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5206,10 +5206,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126867851</v>
+        <v>126862581</v>
       </c>
       <c r="B46" t="n">
-        <v>98464</v>
+        <v>91291</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5217,34 +5217,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699963</v>
+        <v>699816</v>
       </c>
       <c r="R46" t="n">
-        <v>7113120</v>
+        <v>7113390</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5291,12 +5291,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5307,32 +5307,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126862659</v>
+        <v>126862620</v>
       </c>
       <c r="B47" t="n">
-        <v>75121</v>
+        <v>80117</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699845</v>
+        <v>699885</v>
       </c>
       <c r="R47" t="n">
-        <v>7113325</v>
+        <v>7113266</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5408,32 +5408,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126862620</v>
+        <v>126862659</v>
       </c>
       <c r="B48" t="n">
-        <v>80117</v>
+        <v>75121</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>699885</v>
+        <v>699845</v>
       </c>
       <c r="R48" t="n">
-        <v>7113266</v>
+        <v>7113325</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5509,10 +5509,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126862581</v>
+        <v>126867851</v>
       </c>
       <c r="B49" t="n">
-        <v>91291</v>
+        <v>98464</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5520,34 +5520,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>699816</v>
+        <v>699963</v>
       </c>
       <c r="R49" t="n">
-        <v>7113390</v>
+        <v>7113120</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5594,12 +5594,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5610,32 +5610,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126864676</v>
+        <v>126864677</v>
       </c>
       <c r="B50" t="n">
-        <v>91291</v>
+        <v>91326</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>699986</v>
+        <v>699961</v>
       </c>
       <c r="R50" t="n">
-        <v>7113023</v>
+        <v>7113050</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5711,45 +5711,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126867890</v>
+        <v>126862568</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>105463</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>699832</v>
+        <v>699772</v>
       </c>
       <c r="R51" t="n">
-        <v>7113381</v>
+        <v>7113578</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5796,12 +5796,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5812,32 +5812,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126864677</v>
+        <v>126863289</v>
       </c>
       <c r="B52" t="n">
-        <v>91326</v>
+        <v>97321</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>699961</v>
+        <v>699799</v>
       </c>
       <c r="R52" t="n">
-        <v>7113050</v>
+        <v>7113391</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,12 +5897,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5913,10 +5913,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126862568</v>
+        <v>126864676</v>
       </c>
       <c r="B53" t="n">
-        <v>105463</v>
+        <v>91291</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5924,21 +5924,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>699772</v>
+        <v>699986</v>
       </c>
       <c r="R53" t="n">
-        <v>7113578</v>
+        <v>7113023</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5998,12 +5998,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6014,45 +6014,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126863289</v>
+        <v>126867890</v>
       </c>
       <c r="B54" t="n">
-        <v>97321</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>699799</v>
+        <v>699832</v>
       </c>
       <c r="R54" t="n">
-        <v>7113391</v>
+        <v>7113381</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6099,12 +6099,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126864688</v>
+        <v>126862626</v>
       </c>
       <c r="B6" t="n">
-        <v>82855</v>
+        <v>80117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699884</v>
+        <v>699893</v>
       </c>
       <c r="R6" t="n">
-        <v>7113179</v>
+        <v>7113185</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,19 +1217,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1240,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126862626</v>
+        <v>126864688</v>
       </c>
       <c r="B7" t="n">
-        <v>80117</v>
+        <v>82855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1250,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>699893</v>
+        <v>699884</v>
       </c>
       <c r="R7" t="n">
-        <v>7113185</v>
+        <v>7113179</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,18 +1318,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126862622</v>
+        <v>126862590</v>
       </c>
       <c r="B16" t="n">
-        <v>80117</v>
+        <v>57817</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2174,34 +2174,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>699782</v>
+        <v>699877</v>
       </c>
       <c r="R16" t="n">
-        <v>7113622</v>
+        <v>7113231</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2264,10 +2276,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126862590</v>
+        <v>126862622</v>
       </c>
       <c r="B17" t="n">
-        <v>57817</v>
+        <v>80117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,46 +2287,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>699877</v>
+        <v>699782</v>
       </c>
       <c r="R17" t="n">
-        <v>7113231</v>
+        <v>7113622</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3084,32 +3084,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126868058</v>
+        <v>126862598</v>
       </c>
       <c r="B25" t="n">
-        <v>91326</v>
+        <v>98464</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699940</v>
+        <v>699820</v>
       </c>
       <c r="R25" t="n">
-        <v>7113194</v>
+        <v>7113394</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3169,12 +3169,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3185,32 +3185,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126862598</v>
+        <v>126868058</v>
       </c>
       <c r="B26" t="n">
-        <v>98464</v>
+        <v>91326</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699820</v>
+        <v>699940</v>
       </c>
       <c r="R26" t="n">
-        <v>7113394</v>
+        <v>7113194</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3270,12 +3270,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -4499,27 +4499,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126862672</v>
+        <v>126867889</v>
       </c>
       <c r="B39" t="n">
-        <v>80152</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4530,14 +4530,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699843</v>
+        <v>699818</v>
       </c>
       <c r="R39" t="n">
-        <v>7113335</v>
+        <v>7113415</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4600,27 +4600,27 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126867889</v>
+        <v>126862672</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>80152</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4631,14 +4631,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699818</v>
+        <v>699843</v>
       </c>
       <c r="R40" t="n">
-        <v>7113415</v>
+        <v>7113335</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4685,12 +4685,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5610,32 +5610,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126864677</v>
+        <v>126864676</v>
       </c>
       <c r="B50" t="n">
-        <v>91326</v>
+        <v>91291</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>699961</v>
+        <v>699986</v>
       </c>
       <c r="R50" t="n">
-        <v>7113050</v>
+        <v>7113023</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5711,32 +5711,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126862568</v>
+        <v>126864677</v>
       </c>
       <c r="B51" t="n">
-        <v>105463</v>
+        <v>91326</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>699772</v>
+        <v>699961</v>
       </c>
       <c r="R51" t="n">
-        <v>7113578</v>
+        <v>7113050</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5796,12 +5796,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5812,45 +5812,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126863289</v>
+        <v>126867890</v>
       </c>
       <c r="B52" t="n">
-        <v>97321</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>699799</v>
+        <v>699832</v>
       </c>
       <c r="R52" t="n">
-        <v>7113391</v>
+        <v>7113381</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,12 +5897,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5913,10 +5913,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126864676</v>
+        <v>126862568</v>
       </c>
       <c r="B53" t="n">
-        <v>91291</v>
+        <v>105463</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5924,21 +5924,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>699986</v>
+        <v>699772</v>
       </c>
       <c r="R53" t="n">
-        <v>7113023</v>
+        <v>7113578</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5998,12 +5998,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6014,45 +6014,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126867890</v>
+        <v>126863289</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>97321</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>699832</v>
+        <v>699799</v>
       </c>
       <c r="R54" t="n">
-        <v>7113381</v>
+        <v>7113391</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6099,12 +6099,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -5610,32 +5610,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126864676</v>
+        <v>126864677</v>
       </c>
       <c r="B50" t="n">
-        <v>91291</v>
+        <v>91326</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>699986</v>
+        <v>699961</v>
       </c>
       <c r="R50" t="n">
-        <v>7113023</v>
+        <v>7113050</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5711,32 +5711,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126864677</v>
+        <v>126862568</v>
       </c>
       <c r="B51" t="n">
-        <v>91326</v>
+        <v>105463</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>699961</v>
+        <v>699772</v>
       </c>
       <c r="R51" t="n">
-        <v>7113050</v>
+        <v>7113578</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5796,12 +5796,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5812,45 +5812,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126867890</v>
+        <v>126863289</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>97321</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>699832</v>
+        <v>699799</v>
       </c>
       <c r="R52" t="n">
-        <v>7113381</v>
+        <v>7113391</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,12 +5897,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5913,10 +5913,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126862568</v>
+        <v>126864676</v>
       </c>
       <c r="B53" t="n">
-        <v>105463</v>
+        <v>91291</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5924,21 +5924,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>699772</v>
+        <v>699986</v>
       </c>
       <c r="R53" t="n">
-        <v>7113578</v>
+        <v>7113023</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5998,12 +5998,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6014,45 +6014,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126863289</v>
+        <v>126867890</v>
       </c>
       <c r="B54" t="n">
-        <v>97321</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>699799</v>
+        <v>699832</v>
       </c>
       <c r="R54" t="n">
-        <v>7113391</v>
+        <v>7113381</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6099,12 +6099,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126868059</v>
+        <v>126864688</v>
       </c>
       <c r="B5" t="n">
-        <v>91326</v>
+        <v>82859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699956</v>
+        <v>699884</v>
       </c>
       <c r="R5" t="n">
-        <v>7113052</v>
+        <v>7113179</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,18 +1116,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1138,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126862626</v>
+        <v>126868059</v>
       </c>
       <c r="B6" t="n">
-        <v>80117</v>
+        <v>91330</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699893</v>
+        <v>699956</v>
       </c>
       <c r="R6" t="n">
-        <v>7113185</v>
+        <v>7113052</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,12 +1224,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1239,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126864688</v>
+        <v>126862626</v>
       </c>
       <c r="B7" t="n">
-        <v>82855</v>
+        <v>80121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1274,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>699884</v>
+        <v>699893</v>
       </c>
       <c r="R7" t="n">
-        <v>7113179</v>
+        <v>7113185</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,19 +1319,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1344,7 +1344,7 @@
         <v>126862625</v>
       </c>
       <c r="B8" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>126862596</v>
       </c>
       <c r="B9" t="n">
-        <v>99087</v>
+        <v>99091</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126868057</v>
+        <v>126850606</v>
       </c>
       <c r="B10" t="n">
-        <v>91326</v>
+        <v>57821</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,37 +1554,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Nydala, Nydala, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>699944</v>
+        <v>699845</v>
       </c>
       <c r="R10" t="n">
-        <v>7113181</v>
+        <v>7113169</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,26 +1628,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126850606</v>
+        <v>126868057</v>
       </c>
       <c r="B11" t="n">
-        <v>57817</v>
+        <v>91330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,37 +1651,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nydala, Nydala, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>699845</v>
+        <v>699944</v>
       </c>
       <c r="R11" t="n">
-        <v>7113169</v>
+        <v>7113181</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1729,69 +1725,61 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Torbjörn Söderquist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126867857</v>
+        <v>126868067</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>98364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>699822</v>
+        <v>699947</v>
       </c>
       <c r="R12" t="n">
-        <v>7113408</v>
+        <v>7113090</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,25 +1814,29 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 20 st på liten yta</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1855,45 +1847,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126868067</v>
+        <v>126867857</v>
       </c>
       <c r="B13" t="n">
-        <v>98360</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>699947</v>
+        <v>699822</v>
       </c>
       <c r="R13" t="n">
-        <v>7113090</v>
+        <v>7113408</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,29 +1932,25 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ca 20 st på liten yta</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1964,7 +1964,7 @@
         <v>126864681</v>
       </c>
       <c r="B14" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>126862664</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126862590</v>
+        <v>126862622</v>
       </c>
       <c r="B16" t="n">
-        <v>57817</v>
+        <v>80121</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2174,46 +2174,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>699877</v>
+        <v>699782</v>
       </c>
       <c r="R16" t="n">
-        <v>7113231</v>
+        <v>7113622</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2276,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126862622</v>
+        <v>126862590</v>
       </c>
       <c r="B17" t="n">
-        <v>80117</v>
+        <v>57821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,34 +2275,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>699782</v>
+        <v>699877</v>
       </c>
       <c r="R17" t="n">
-        <v>7113622</v>
+        <v>7113231</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2380,7 @@
         <v>126867850</v>
       </c>
       <c r="B18" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>126867848</v>
       </c>
       <c r="B19" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>126868062</v>
       </c>
       <c r="B20" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>126864675</v>
       </c>
       <c r="B21" t="n">
-        <v>96696</v>
+        <v>96700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126862624</v>
+        <v>126863282</v>
       </c>
       <c r="B22" t="n">
-        <v>80117</v>
+        <v>91330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2792,21 +2792,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>699857</v>
+        <v>699958</v>
       </c>
       <c r="R22" t="n">
-        <v>7113431</v>
+        <v>7113052</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,12 +2866,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2882,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126863282</v>
+        <v>126862599</v>
       </c>
       <c r="B23" t="n">
-        <v>91326</v>
+        <v>80122</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2893,21 +2893,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>699958</v>
+        <v>699778</v>
       </c>
       <c r="R23" t="n">
-        <v>7113052</v>
+        <v>7113628</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2967,12 +2967,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2983,10 +2983,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126862599</v>
+        <v>126862624</v>
       </c>
       <c r="B24" t="n">
-        <v>80118</v>
+        <v>80121</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2994,21 +2994,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>699778</v>
+        <v>699857</v>
       </c>
       <c r="R24" t="n">
-        <v>7113628</v>
+        <v>7113431</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,32 +3084,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126862598</v>
+        <v>126868058</v>
       </c>
       <c r="B25" t="n">
-        <v>98464</v>
+        <v>91330</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699820</v>
+        <v>699940</v>
       </c>
       <c r="R25" t="n">
-        <v>7113394</v>
+        <v>7113194</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3169,12 +3169,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3185,32 +3185,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126868058</v>
+        <v>126862598</v>
       </c>
       <c r="B26" t="n">
-        <v>91326</v>
+        <v>98468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699940</v>
+        <v>699820</v>
       </c>
       <c r="R26" t="n">
-        <v>7113194</v>
+        <v>7113394</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3270,12 +3270,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3286,10 +3286,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126862627</v>
+        <v>126862669</v>
       </c>
       <c r="B27" t="n">
-        <v>80153</v>
+        <v>98364</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3297,21 +3297,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699788</v>
+        <v>699879</v>
       </c>
       <c r="R27" t="n">
-        <v>7113541</v>
+        <v>7113265</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126862570</v>
+        <v>126867894</v>
       </c>
       <c r="B28" t="n">
-        <v>105463</v>
+        <v>98364</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,34 +3398,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221725</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699830</v>
+        <v>699948</v>
       </c>
       <c r="R28" t="n">
-        <v>7113371</v>
+        <v>7113110</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,12 +3472,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3488,10 +3488,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126862669</v>
+        <v>126862570</v>
       </c>
       <c r="B29" t="n">
-        <v>98360</v>
+        <v>105469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,21 +3499,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>221725</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699879</v>
+        <v>699830</v>
       </c>
       <c r="R29" t="n">
-        <v>7113265</v>
+        <v>7113371</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126867894</v>
+        <v>126862627</v>
       </c>
       <c r="B30" t="n">
-        <v>98360</v>
+        <v>80157</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3600,34 +3600,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699948</v>
+        <v>699788</v>
       </c>
       <c r="R30" t="n">
-        <v>7113110</v>
+        <v>7113541</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3674,12 +3674,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3693,7 +3693,7 @@
         <v>126864689</v>
       </c>
       <c r="B31" t="n">
-        <v>82855</v>
+        <v>82859</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>126867883</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3893,10 +3893,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126867886</v>
+        <v>126863288</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>91626</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3904,34 +3904,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699878</v>
+        <v>699939</v>
       </c>
       <c r="R33" t="n">
-        <v>7113551</v>
+        <v>7113199</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3978,12 +3978,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3994,10 +3994,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126863288</v>
+        <v>126867886</v>
       </c>
       <c r="B34" t="n">
-        <v>91622</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4005,34 +4005,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699939</v>
+        <v>699878</v>
       </c>
       <c r="R34" t="n">
-        <v>7113199</v>
+        <v>7113551</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4079,12 +4079,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4098,7 +4098,7 @@
         <v>126862623</v>
       </c>
       <c r="B35" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>126863291</v>
       </c>
       <c r="B36" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>126867844</v>
       </c>
       <c r="B37" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>126868055</v>
       </c>
       <c r="B38" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>126867889</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>126862672</v>
       </c>
       <c r="B40" t="n">
-        <v>80152</v>
+        <v>80156</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>126867887</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4802,32 +4802,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126862628</v>
+        <v>126862671</v>
       </c>
       <c r="B42" t="n">
-        <v>80117</v>
+        <v>98364</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699783</v>
+        <v>699946</v>
       </c>
       <c r="R42" t="n">
-        <v>7113533</v>
+        <v>7113098</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4906,7 +4906,7 @@
         <v>126867884</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>126862595</v>
       </c>
       <c r="B44" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5105,32 +5105,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126862671</v>
+        <v>126862628</v>
       </c>
       <c r="B45" t="n">
-        <v>98360</v>
+        <v>80121</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699946</v>
+        <v>699783</v>
       </c>
       <c r="R45" t="n">
-        <v>7113098</v>
+        <v>7113533</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5209,7 +5209,7 @@
         <v>126862581</v>
       </c>
       <c r="B46" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>126862620</v>
       </c>
       <c r="B47" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>126862659</v>
       </c>
       <c r="B48" t="n">
-        <v>75121</v>
+        <v>75125</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>126867851</v>
       </c>
       <c r="B49" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>126864677</v>
       </c>
       <c r="B50" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5711,10 +5711,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126862568</v>
+        <v>126864676</v>
       </c>
       <c r="B51" t="n">
-        <v>105463</v>
+        <v>91295</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>699772</v>
+        <v>699986</v>
       </c>
       <c r="R51" t="n">
-        <v>7113578</v>
+        <v>7113023</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5796,12 +5796,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5812,45 +5812,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126863289</v>
+        <v>126867890</v>
       </c>
       <c r="B52" t="n">
-        <v>97321</v>
+        <v>79018</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>699799</v>
+        <v>699832</v>
       </c>
       <c r="R52" t="n">
-        <v>7113391</v>
+        <v>7113381</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,12 +5897,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5913,10 +5913,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126864676</v>
+        <v>126862568</v>
       </c>
       <c r="B53" t="n">
-        <v>91291</v>
+        <v>105469</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5924,21 +5924,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>699986</v>
+        <v>699772</v>
       </c>
       <c r="R53" t="n">
-        <v>7113023</v>
+        <v>7113578</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5998,12 +5998,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6014,45 +6014,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126867890</v>
+        <v>126863289</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>97325</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>699832</v>
+        <v>699799</v>
       </c>
       <c r="R54" t="n">
-        <v>7113381</v>
+        <v>7113391</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6099,12 +6099,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6118,7 +6118,7 @@
         <v>126863287</v>
       </c>
       <c r="B55" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>126867837</v>
       </c>
       <c r="B56" t="n">
-        <v>105463</v>
+        <v>105469</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>126864684</v>
       </c>
       <c r="B57" t="n">
-        <v>78418</v>
+        <v>78422</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -1543,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126850606</v>
+        <v>126868057</v>
       </c>
       <c r="B10" t="n">
-        <v>57821</v>
+        <v>91330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,37 +1554,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nydala, Nydala, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>699845</v>
+        <v>699944</v>
       </c>
       <c r="R10" t="n">
-        <v>7113169</v>
+        <v>7113181</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,44 +1628,48 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Torbjörn Söderquist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126868057</v>
+        <v>126868067</v>
       </c>
       <c r="B11" t="n">
-        <v>91330</v>
+        <v>98364</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1675,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>699944</v>
+        <v>699947</v>
       </c>
       <c r="R11" t="n">
-        <v>7113181</v>
+        <v>7113090</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,6 +1715,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca 20 st på liten yta</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,45 +1750,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126868067</v>
+        <v>126867857</v>
       </c>
       <c r="B12" t="n">
-        <v>98364</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>699947</v>
+        <v>699822</v>
       </c>
       <c r="R12" t="n">
-        <v>7113090</v>
+        <v>7113408</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,29 +1835,25 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 20 st på liten yta</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1847,60 +1864,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126867857</v>
+        <v>126850606</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>57821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Nydala, Nydala, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>699822</v>
+        <v>699845</v>
       </c>
       <c r="R13" t="n">
-        <v>7113408</v>
+        <v>7113169</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1938,7 +1943,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1953,18 +1957,14 @@
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126864681</v>
+        <v>126862664</v>
       </c>
       <c r="B14" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,21 +1972,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>699880</v>
+        <v>699735</v>
       </c>
       <c r="R14" t="n">
-        <v>7113259</v>
+        <v>7113552</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,12 +2046,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126862664</v>
+        <v>126864681</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,21 +2073,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>699735</v>
+        <v>699880</v>
       </c>
       <c r="R15" t="n">
-        <v>7113552</v>
+        <v>7113259</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,12 +2147,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2377,45 +2377,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126867850</v>
+        <v>126868062</v>
       </c>
       <c r="B18" t="n">
-        <v>98468</v>
+        <v>57821</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>699955</v>
+        <v>699845</v>
       </c>
       <c r="R18" t="n">
-        <v>7113130</v>
+        <v>7113187</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,12 +2462,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2478,7 +2478,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126867848</v>
+        <v>126867850</v>
       </c>
       <c r="B19" t="n">
         <v>98468</v>
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>699755</v>
+        <v>699955</v>
       </c>
       <c r="R19" t="n">
-        <v>7113586</v>
+        <v>7113130</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,45 +2579,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126868062</v>
+        <v>126867848</v>
       </c>
       <c r="B20" t="n">
-        <v>57821</v>
+        <v>98468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>699845</v>
+        <v>699755</v>
       </c>
       <c r="R20" t="n">
-        <v>7113187</v>
+        <v>7113586</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,12 +2664,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3286,10 +3286,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126862669</v>
+        <v>126862627</v>
       </c>
       <c r="B27" t="n">
-        <v>98364</v>
+        <v>80157</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3297,21 +3297,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699879</v>
+        <v>699788</v>
       </c>
       <c r="R27" t="n">
-        <v>7113265</v>
+        <v>7113541</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126867894</v>
+        <v>126862570</v>
       </c>
       <c r="B28" t="n">
-        <v>98364</v>
+        <v>105469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,34 +3398,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>221725</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699948</v>
+        <v>699830</v>
       </c>
       <c r="R28" t="n">
-        <v>7113110</v>
+        <v>7113371</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,12 +3472,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3488,10 +3488,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126862570</v>
+        <v>126862669</v>
       </c>
       <c r="B29" t="n">
-        <v>105469</v>
+        <v>98364</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,21 +3499,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221725</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699830</v>
+        <v>699879</v>
       </c>
       <c r="R29" t="n">
-        <v>7113371</v>
+        <v>7113265</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126862627</v>
+        <v>126867894</v>
       </c>
       <c r="B30" t="n">
-        <v>80157</v>
+        <v>98364</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3600,34 +3600,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699788</v>
+        <v>699948</v>
       </c>
       <c r="R30" t="n">
-        <v>7113541</v>
+        <v>7113110</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3674,12 +3674,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4398,45 +4398,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126868055</v>
+        <v>126867889</v>
       </c>
       <c r="B38" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699981</v>
+        <v>699818</v>
       </c>
       <c r="R38" t="n">
-        <v>7113021</v>
+        <v>7113415</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4483,12 +4483,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4499,45 +4499,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126867889</v>
+        <v>126868055</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699818</v>
+        <v>699981</v>
       </c>
       <c r="R39" t="n">
-        <v>7113415</v>
+        <v>7113021</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4802,10 +4802,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126862671</v>
+        <v>126862595</v>
       </c>
       <c r="B42" t="n">
-        <v>98364</v>
+        <v>80150</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699946</v>
+        <v>699848</v>
       </c>
       <c r="R42" t="n">
-        <v>7113098</v>
+        <v>7113330</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4903,10 +4903,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126867884</v>
+        <v>126862628</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4914,34 +4914,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699877</v>
+        <v>699783</v>
       </c>
       <c r="R43" t="n">
-        <v>7113569</v>
+        <v>7113533</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4988,12 +4988,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5004,45 +5004,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126862595</v>
+        <v>126867884</v>
       </c>
       <c r="B44" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699848</v>
+        <v>699877</v>
       </c>
       <c r="R44" t="n">
-        <v>7113330</v>
+        <v>7113569</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5089,12 +5089,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5105,32 +5105,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126862628</v>
+        <v>126862671</v>
       </c>
       <c r="B45" t="n">
-        <v>80121</v>
+        <v>98364</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699783</v>
+        <v>699946</v>
       </c>
       <c r="R45" t="n">
-        <v>7113533</v>
+        <v>7113098</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5206,32 +5206,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126862581</v>
+        <v>126862620</v>
       </c>
       <c r="B46" t="n">
-        <v>91295</v>
+        <v>80121</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5241,10 +5241,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699816</v>
+        <v>699885</v>
       </c>
       <c r="R46" t="n">
-        <v>7113390</v>
+        <v>7113266</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5307,45 +5307,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126862620</v>
+        <v>126867851</v>
       </c>
       <c r="B47" t="n">
-        <v>80121</v>
+        <v>98468</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699885</v>
+        <v>699963</v>
       </c>
       <c r="R47" t="n">
-        <v>7113266</v>
+        <v>7113120</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,12 +5392,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5509,10 +5509,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126867851</v>
+        <v>126862581</v>
       </c>
       <c r="B49" t="n">
-        <v>98468</v>
+        <v>91295</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5520,34 +5520,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>699963</v>
+        <v>699816</v>
       </c>
       <c r="R49" t="n">
-        <v>7113120</v>
+        <v>7113390</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5594,12 +5594,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -1644,48 +1644,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126868067</v>
+        <v>126850606</v>
       </c>
       <c r="B11" t="n">
-        <v>98364</v>
+        <v>57821</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Nydala, Nydala, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>699947</v>
+        <v>699845</v>
       </c>
       <c r="R11" t="n">
-        <v>7113090</v>
+        <v>7113169</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1715,11 +1715,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca 20 st på liten yta</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,73 +1729,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126867857</v>
+        <v>126868067</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>699822</v>
+        <v>699947</v>
       </c>
       <c r="R12" t="n">
-        <v>7113408</v>
+        <v>7113090</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,25 +1814,29 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 20 st på liten yta</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1864,48 +1847,60 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126850606</v>
+        <v>126867857</v>
       </c>
       <c r="B13" t="n">
-        <v>57821</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nydala, Nydala, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>699845</v>
+        <v>699822</v>
       </c>
       <c r="R13" t="n">
-        <v>7113169</v>
+        <v>7113408</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1943,6 +1938,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1957,14 +1953,18 @@
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126862664</v>
+        <v>126864681</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,21 +1972,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>699735</v>
+        <v>699880</v>
       </c>
       <c r="R14" t="n">
-        <v>7113552</v>
+        <v>7113259</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,12 +2046,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126864681</v>
+        <v>126862664</v>
       </c>
       <c r="B15" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,21 +2073,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>699880</v>
+        <v>699735</v>
       </c>
       <c r="R15" t="n">
-        <v>7113259</v>
+        <v>7113552</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,12 +2147,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -3286,10 +3286,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126862627</v>
+        <v>126862570</v>
       </c>
       <c r="B27" t="n">
-        <v>80157</v>
+        <v>105469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3297,21 +3297,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>221725</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699788</v>
+        <v>699830</v>
       </c>
       <c r="R27" t="n">
-        <v>7113541</v>
+        <v>7113371</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126862570</v>
+        <v>126862669</v>
       </c>
       <c r="B28" t="n">
-        <v>105469</v>
+        <v>98364</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,21 +3398,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221725</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699830</v>
+        <v>699879</v>
       </c>
       <c r="R28" t="n">
-        <v>7113371</v>
+        <v>7113265</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126862669</v>
+        <v>126867894</v>
       </c>
       <c r="B29" t="n">
         <v>98364</v>
@@ -3519,14 +3519,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699879</v>
+        <v>699948</v>
       </c>
       <c r="R29" t="n">
-        <v>7113265</v>
+        <v>7113110</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3573,12 +3573,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126867894</v>
+        <v>126862627</v>
       </c>
       <c r="B30" t="n">
-        <v>98364</v>
+        <v>80157</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3600,34 +3600,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699948</v>
+        <v>699788</v>
       </c>
       <c r="R30" t="n">
-        <v>7113110</v>
+        <v>7113541</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3674,12 +3674,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -5206,32 +5206,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126862620</v>
+        <v>126862581</v>
       </c>
       <c r="B46" t="n">
-        <v>80121</v>
+        <v>91295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5241,10 +5241,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699885</v>
+        <v>699816</v>
       </c>
       <c r="R46" t="n">
-        <v>7113266</v>
+        <v>7113390</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5307,45 +5307,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126867851</v>
+        <v>126862620</v>
       </c>
       <c r="B47" t="n">
-        <v>98468</v>
+        <v>80121</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699963</v>
+        <v>699885</v>
       </c>
       <c r="R47" t="n">
-        <v>7113120</v>
+        <v>7113266</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,12 +5392,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5408,10 +5408,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126862659</v>
+        <v>126867851</v>
       </c>
       <c r="B48" t="n">
-        <v>75125</v>
+        <v>98468</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5419,34 +5419,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6439</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>699845</v>
+        <v>699963</v>
       </c>
       <c r="R48" t="n">
-        <v>7113325</v>
+        <v>7113120</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5493,12 +5493,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5509,10 +5509,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126862581</v>
+        <v>126862659</v>
       </c>
       <c r="B49" t="n">
-        <v>91295</v>
+        <v>75125</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5520,21 +5520,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>6439</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>699816</v>
+        <v>699845</v>
       </c>
       <c r="R49" t="n">
-        <v>7113390</v>
+        <v>7113325</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126864688</v>
+        <v>126862626</v>
       </c>
       <c r="B5" t="n">
-        <v>82859</v>
+        <v>80121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699884</v>
+        <v>699893</v>
       </c>
       <c r="R5" t="n">
-        <v>7113179</v>
+        <v>7113185</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,19 +1116,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1139,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126868059</v>
+        <v>126864688</v>
       </c>
       <c r="B6" t="n">
-        <v>91330</v>
+        <v>82859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699956</v>
+        <v>699884</v>
       </c>
       <c r="R6" t="n">
-        <v>7113052</v>
+        <v>7113179</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,18 +1217,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126862626</v>
+        <v>126868059</v>
       </c>
       <c r="B7" t="n">
-        <v>80121</v>
+        <v>91330</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>699893</v>
+        <v>699956</v>
       </c>
       <c r="R7" t="n">
-        <v>7113185</v>
+        <v>7113052</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,12 +1325,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1543,32 +1543,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126868057</v>
+        <v>126868067</v>
       </c>
       <c r="B10" t="n">
-        <v>91330</v>
+        <v>98364</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>699944</v>
+        <v>699947</v>
       </c>
       <c r="R10" t="n">
-        <v>7113181</v>
+        <v>7113090</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,6 +1614,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca 20 st på liten yta</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,48 +1649,60 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126850606</v>
+        <v>126867857</v>
       </c>
       <c r="B11" t="n">
-        <v>57821</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nydala, Nydala, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>699845</v>
+        <v>699822</v>
       </c>
       <c r="R11" t="n">
-        <v>7113169</v>
+        <v>7113408</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1723,6 +1740,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1737,52 +1755,56 @@
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126868067</v>
+        <v>126850606</v>
       </c>
       <c r="B12" t="n">
-        <v>98364</v>
+        <v>57821</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Nydala, Nydala, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>699947</v>
+        <v>699845</v>
       </c>
       <c r="R12" t="n">
-        <v>7113090</v>
+        <v>7113169</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1812,11 +1834,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 20 st på liten yta</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1831,73 +1848,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126867857</v>
+        <v>126868057</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>699822</v>
+        <v>699944</v>
       </c>
       <c r="R13" t="n">
-        <v>7113408</v>
+        <v>7113181</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,19 +1939,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1961,10 +1961,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126864681</v>
+        <v>126862664</v>
       </c>
       <c r="B14" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,21 +1972,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>699880</v>
+        <v>699735</v>
       </c>
       <c r="R14" t="n">
-        <v>7113259</v>
+        <v>7113552</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,12 +2046,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126862664</v>
+        <v>126864681</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,21 +2073,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>699735</v>
+        <v>699880</v>
       </c>
       <c r="R15" t="n">
-        <v>7113552</v>
+        <v>7113259</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,12 +2147,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2377,45 +2377,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126868062</v>
+        <v>126867850</v>
       </c>
       <c r="B18" t="n">
-        <v>57821</v>
+        <v>98468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>699845</v>
+        <v>699955</v>
       </c>
       <c r="R18" t="n">
-        <v>7113187</v>
+        <v>7113130</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,12 +2462,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2478,7 +2478,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126867850</v>
+        <v>126867848</v>
       </c>
       <c r="B19" t="n">
         <v>98468</v>
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>699955</v>
+        <v>699755</v>
       </c>
       <c r="R19" t="n">
-        <v>7113130</v>
+        <v>7113586</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,45 +2579,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126867848</v>
+        <v>126868062</v>
       </c>
       <c r="B20" t="n">
-        <v>98468</v>
+        <v>57821</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>699755</v>
+        <v>699845</v>
       </c>
       <c r="R20" t="n">
-        <v>7113586</v>
+        <v>7113187</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,12 +2664,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -4802,10 +4802,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126862595</v>
+        <v>126862671</v>
       </c>
       <c r="B42" t="n">
-        <v>80150</v>
+        <v>98364</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699848</v>
+        <v>699946</v>
       </c>
       <c r="R42" t="n">
-        <v>7113330</v>
+        <v>7113098</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4903,32 +4903,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126862628</v>
+        <v>126862595</v>
       </c>
       <c r="B43" t="n">
-        <v>80121</v>
+        <v>80150</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699783</v>
+        <v>699848</v>
       </c>
       <c r="R43" t="n">
-        <v>7113533</v>
+        <v>7113330</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5004,10 +5004,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126867884</v>
+        <v>126862628</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5015,34 +5015,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699877</v>
+        <v>699783</v>
       </c>
       <c r="R44" t="n">
-        <v>7113569</v>
+        <v>7113533</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5089,12 +5089,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5105,45 +5105,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126862671</v>
+        <v>126867884</v>
       </c>
       <c r="B45" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699946</v>
+        <v>699877</v>
       </c>
       <c r="R45" t="n">
-        <v>7113098</v>
+        <v>7113569</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5190,12 +5190,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126862626</v>
+        <v>126868059</v>
       </c>
       <c r="B5" t="n">
-        <v>80121</v>
+        <v>91330</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699893</v>
+        <v>699956</v>
       </c>
       <c r="R5" t="n">
-        <v>7113185</v>
+        <v>7113052</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,12 +1122,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126868059</v>
+        <v>126862626</v>
       </c>
       <c r="B7" t="n">
-        <v>91330</v>
+        <v>80121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>699956</v>
+        <v>699893</v>
       </c>
       <c r="R7" t="n">
-        <v>7113052</v>
+        <v>7113185</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,12 +1325,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1445,7 +1445,7 @@
         <v>126862596</v>
       </c>
       <c r="B9" t="n">
-        <v>99091</v>
+        <v>99092</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1543,32 +1543,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126868067</v>
+        <v>126868057</v>
       </c>
       <c r="B10" t="n">
-        <v>98364</v>
+        <v>91330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>699947</v>
+        <v>699944</v>
       </c>
       <c r="R10" t="n">
-        <v>7113090</v>
+        <v>7113181</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,11 +1614,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ca 20 st på liten yta</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,60 +1644,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126867857</v>
+        <v>126850606</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>57821</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Nydala, Nydala, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>699822</v>
+        <v>699845</v>
       </c>
       <c r="R11" t="n">
-        <v>7113408</v>
+        <v>7113169</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1740,7 +1723,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1755,56 +1737,52 @@
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126850606</v>
+        <v>126868067</v>
       </c>
       <c r="B12" t="n">
-        <v>57821</v>
+        <v>98365</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nydala, Nydala, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>699845</v>
+        <v>699947</v>
       </c>
       <c r="R12" t="n">
-        <v>7113169</v>
+        <v>7113090</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1834,6 +1812,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 20 st på liten yta</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,57 +1831,73 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Torbjörn Söderquist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126868057</v>
+        <v>126867857</v>
       </c>
       <c r="B13" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>699944</v>
+        <v>699822</v>
       </c>
       <c r="R13" t="n">
-        <v>7113181</v>
+        <v>7113408</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,18 +1938,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2380,7 +2380,7 @@
         <v>126867850</v>
       </c>
       <c r="B18" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>126867848</v>
       </c>
       <c r="B19" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3084,32 +3084,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126868058</v>
+        <v>126862598</v>
       </c>
       <c r="B25" t="n">
-        <v>91330</v>
+        <v>98469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699940</v>
+        <v>699820</v>
       </c>
       <c r="R25" t="n">
-        <v>7113194</v>
+        <v>7113394</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3169,12 +3169,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3185,32 +3185,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126862598</v>
+        <v>126868058</v>
       </c>
       <c r="B26" t="n">
-        <v>98468</v>
+        <v>91330</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699820</v>
+        <v>699940</v>
       </c>
       <c r="R26" t="n">
-        <v>7113394</v>
+        <v>7113194</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3270,12 +3270,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3286,10 +3286,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126862570</v>
+        <v>126862669</v>
       </c>
       <c r="B27" t="n">
-        <v>105469</v>
+        <v>98365</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3297,21 +3297,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221725</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699830</v>
+        <v>699879</v>
       </c>
       <c r="R27" t="n">
-        <v>7113371</v>
+        <v>7113265</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126862669</v>
+        <v>126867894</v>
       </c>
       <c r="B28" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3418,14 +3418,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699879</v>
+        <v>699948</v>
       </c>
       <c r="R28" t="n">
-        <v>7113265</v>
+        <v>7113110</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,12 +3472,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3488,10 +3488,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126867894</v>
+        <v>126862570</v>
       </c>
       <c r="B29" t="n">
-        <v>98364</v>
+        <v>105471</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>221725</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699948</v>
+        <v>699830</v>
       </c>
       <c r="R29" t="n">
-        <v>7113110</v>
+        <v>7113371</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3573,12 +3573,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3690,10 +3690,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126864689</v>
+        <v>126867883</v>
       </c>
       <c r="B31" t="n">
-        <v>82859</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3701,34 +3701,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699933</v>
+        <v>699804</v>
       </c>
       <c r="R31" t="n">
-        <v>7113088</v>
+        <v>7113653</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3769,19 +3769,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3792,10 +3791,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126867883</v>
+        <v>126864689</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>82859</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3803,34 +3802,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699804</v>
+        <v>699933</v>
       </c>
       <c r="R32" t="n">
-        <v>7113653</v>
+        <v>7113088</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3871,18 +3870,19 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4499,10 +4499,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126868055</v>
+        <v>126862672</v>
       </c>
       <c r="B39" t="n">
-        <v>91295</v>
+        <v>80156</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699981</v>
+        <v>699843</v>
       </c>
       <c r="R39" t="n">
-        <v>7113021</v>
+        <v>7113335</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4600,10 +4600,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126862672</v>
+        <v>126868055</v>
       </c>
       <c r="B40" t="n">
-        <v>80156</v>
+        <v>91295</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4611,21 +4611,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699843</v>
+        <v>699981</v>
       </c>
       <c r="R40" t="n">
-        <v>7113335</v>
+        <v>7113021</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4685,12 +4685,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4802,45 +4802,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126862671</v>
+        <v>126867884</v>
       </c>
       <c r="B42" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699946</v>
+        <v>699877</v>
       </c>
       <c r="R42" t="n">
-        <v>7113098</v>
+        <v>7113569</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4887,12 +4887,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5105,45 +5105,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126867884</v>
+        <v>126862671</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>98365</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699877</v>
+        <v>699946</v>
       </c>
       <c r="R45" t="n">
-        <v>7113569</v>
+        <v>7113098</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5190,12 +5190,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5206,10 +5206,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126862581</v>
+        <v>126867851</v>
       </c>
       <c r="B46" t="n">
-        <v>91295</v>
+        <v>98469</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5217,34 +5217,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699816</v>
+        <v>699963</v>
       </c>
       <c r="R46" t="n">
-        <v>7113390</v>
+        <v>7113120</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5291,12 +5291,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5307,32 +5307,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126862620</v>
+        <v>126862659</v>
       </c>
       <c r="B47" t="n">
-        <v>80121</v>
+        <v>75125</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699885</v>
+        <v>699845</v>
       </c>
       <c r="R47" t="n">
-        <v>7113266</v>
+        <v>7113325</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5408,45 +5408,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126867851</v>
+        <v>126862620</v>
       </c>
       <c r="B48" t="n">
-        <v>98468</v>
+        <v>80121</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>699963</v>
+        <v>699885</v>
       </c>
       <c r="R48" t="n">
-        <v>7113120</v>
+        <v>7113266</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5493,12 +5493,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5509,10 +5509,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126862659</v>
+        <v>126862581</v>
       </c>
       <c r="B49" t="n">
-        <v>75125</v>
+        <v>91295</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5520,21 +5520,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6439</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>699845</v>
+        <v>699816</v>
       </c>
       <c r="R49" t="n">
-        <v>7113325</v>
+        <v>7113390</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5610,32 +5610,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126864677</v>
+        <v>126862568</v>
       </c>
       <c r="B50" t="n">
-        <v>91330</v>
+        <v>105471</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>699961</v>
+        <v>699772</v>
       </c>
       <c r="R50" t="n">
-        <v>7113050</v>
+        <v>7113578</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5695,12 +5695,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5711,10 +5711,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126864676</v>
+        <v>126863289</v>
       </c>
       <c r="B51" t="n">
-        <v>91295</v>
+        <v>97325</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>699986</v>
+        <v>699799</v>
       </c>
       <c r="R51" t="n">
-        <v>7113023</v>
+        <v>7113391</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5796,12 +5796,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5812,10 +5812,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126867890</v>
+        <v>126864677</v>
       </c>
       <c r="B52" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5823,34 +5823,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>699832</v>
+        <v>699961</v>
       </c>
       <c r="R52" t="n">
-        <v>7113381</v>
+        <v>7113050</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,12 +5897,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5913,45 +5913,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126862568</v>
+        <v>126867890</v>
       </c>
       <c r="B53" t="n">
-        <v>105469</v>
+        <v>79018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>699772</v>
+        <v>699832</v>
       </c>
       <c r="R53" t="n">
-        <v>7113578</v>
+        <v>7113381</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5998,12 +5998,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6014,10 +6014,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126863289</v>
+        <v>126864676</v>
       </c>
       <c r="B54" t="n">
-        <v>97325</v>
+        <v>91295</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6025,21 +6025,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6049,10 +6049,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>699799</v>
+        <v>699986</v>
       </c>
       <c r="R54" t="n">
-        <v>7113391</v>
+        <v>7113023</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6099,12 +6099,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6219,7 +6219,7 @@
         <v>126867837</v>
       </c>
       <c r="B56" t="n">
-        <v>105469</v>
+        <v>105471</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126868059</v>
+        <v>126864688</v>
       </c>
       <c r="B5" t="n">
-        <v>91330</v>
+        <v>82859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699956</v>
+        <v>699884</v>
       </c>
       <c r="R5" t="n">
-        <v>7113052</v>
+        <v>7113179</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,18 +1116,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1138,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126864688</v>
+        <v>126868059</v>
       </c>
       <c r="B6" t="n">
-        <v>82859</v>
+        <v>91330</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699884</v>
+        <v>699956</v>
       </c>
       <c r="R6" t="n">
-        <v>7113179</v>
+        <v>7113052</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,19 +1218,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -2377,45 +2377,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126867850</v>
+        <v>126868062</v>
       </c>
       <c r="B18" t="n">
-        <v>98469</v>
+        <v>57821</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>699955</v>
+        <v>699845</v>
       </c>
       <c r="R18" t="n">
-        <v>7113130</v>
+        <v>7113187</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,12 +2462,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2478,7 +2478,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126867848</v>
+        <v>126867850</v>
       </c>
       <c r="B19" t="n">
         <v>98469</v>
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>699755</v>
+        <v>699955</v>
       </c>
       <c r="R19" t="n">
-        <v>7113586</v>
+        <v>7113130</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,45 +2579,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126868062</v>
+        <v>126867848</v>
       </c>
       <c r="B20" t="n">
-        <v>57821</v>
+        <v>98469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>699845</v>
+        <v>699755</v>
       </c>
       <c r="R20" t="n">
-        <v>7113187</v>
+        <v>7113586</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,12 +2664,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3286,10 +3286,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126862669</v>
+        <v>126862627</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
+        <v>80157</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3297,21 +3297,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699879</v>
+        <v>699788</v>
       </c>
       <c r="R27" t="n">
-        <v>7113265</v>
+        <v>7113541</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3387,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126867894</v>
+        <v>126862570</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,34 +3398,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>221725</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699948</v>
+        <v>699830</v>
       </c>
       <c r="R28" t="n">
-        <v>7113110</v>
+        <v>7113371</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,12 +3472,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3488,10 +3488,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126862570</v>
+        <v>126862669</v>
       </c>
       <c r="B29" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,21 +3499,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221725</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699830</v>
+        <v>699879</v>
       </c>
       <c r="R29" t="n">
-        <v>7113371</v>
+        <v>7113265</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126862627</v>
+        <v>126867894</v>
       </c>
       <c r="B30" t="n">
-        <v>80157</v>
+        <v>98365</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3600,34 +3600,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699788</v>
+        <v>699948</v>
       </c>
       <c r="R30" t="n">
-        <v>7113541</v>
+        <v>7113110</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3674,12 +3674,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4398,27 +4398,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126867889</v>
+        <v>126862672</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>80156</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4429,14 +4429,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699818</v>
+        <v>699843</v>
       </c>
       <c r="R38" t="n">
-        <v>7113415</v>
+        <v>7113335</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4483,12 +4483,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4499,10 +4499,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126862672</v>
+        <v>126868055</v>
       </c>
       <c r="B39" t="n">
-        <v>80156</v>
+        <v>91295</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699843</v>
+        <v>699981</v>
       </c>
       <c r="R39" t="n">
-        <v>7113335</v>
+        <v>7113021</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4600,45 +4600,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126868055</v>
+        <v>126867889</v>
       </c>
       <c r="B40" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699981</v>
+        <v>699818</v>
       </c>
       <c r="R40" t="n">
-        <v>7113021</v>
+        <v>7113415</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4685,12 +4685,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5610,32 +5610,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126862568</v>
+        <v>126864677</v>
       </c>
       <c r="B50" t="n">
-        <v>105471</v>
+        <v>91330</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>699772</v>
+        <v>699961</v>
       </c>
       <c r="R50" t="n">
-        <v>7113578</v>
+        <v>7113050</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5695,12 +5695,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5711,45 +5711,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126863289</v>
+        <v>126867890</v>
       </c>
       <c r="B51" t="n">
-        <v>97325</v>
+        <v>79018</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>699799</v>
+        <v>699832</v>
       </c>
       <c r="R51" t="n">
-        <v>7113391</v>
+        <v>7113381</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5796,12 +5796,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5812,32 +5812,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126864677</v>
+        <v>126864676</v>
       </c>
       <c r="B52" t="n">
-        <v>91330</v>
+        <v>91295</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>699961</v>
+        <v>699986</v>
       </c>
       <c r="R52" t="n">
-        <v>7113050</v>
+        <v>7113023</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5913,45 +5913,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126867890</v>
+        <v>126862568</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>105471</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>699832</v>
+        <v>699772</v>
       </c>
       <c r="R53" t="n">
-        <v>7113381</v>
+        <v>7113578</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5998,12 +5998,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6014,10 +6014,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126864676</v>
+        <v>126863289</v>
       </c>
       <c r="B54" t="n">
-        <v>91295</v>
+        <v>97325</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6025,21 +6025,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6049,10 +6049,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>699986</v>
+        <v>699799</v>
       </c>
       <c r="R54" t="n">
-        <v>7113023</v>
+        <v>7113391</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6099,12 +6099,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -6219,7 +6219,7 @@
         <v>126867837</v>
       </c>
       <c r="B56" t="n">
-        <v>105471</v>
+        <v>105473</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>126864684</v>
       </c>
       <c r="B57" t="n">
-        <v>78422</v>
+        <v>78424</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126864688</v>
+        <v>126862626</v>
       </c>
       <c r="B5" t="n">
-        <v>82859</v>
+        <v>80114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699884</v>
+        <v>699893</v>
       </c>
       <c r="R5" t="n">
-        <v>7113179</v>
+        <v>7113185</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,19 +1116,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1142,7 +1141,7 @@
         <v>126868059</v>
       </c>
       <c r="B6" t="n">
-        <v>91330</v>
+        <v>91319</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126862626</v>
+        <v>126864688</v>
       </c>
       <c r="B7" t="n">
-        <v>80121</v>
+        <v>82852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1250,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>699893</v>
+        <v>699884</v>
       </c>
       <c r="R7" t="n">
-        <v>7113185</v>
+        <v>7113179</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,18 +1318,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1344,7 +1344,7 @@
         <v>126862625</v>
       </c>
       <c r="B8" t="n">
-        <v>80121</v>
+        <v>80114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1445,7 +1445,7 @@
         <v>126862596</v>
       </c>
       <c r="B9" t="n">
-        <v>99092</v>
+        <v>99080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1546,7 +1546,7 @@
         <v>126868057</v>
       </c>
       <c r="B10" t="n">
-        <v>91330</v>
+        <v>91319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>126850606</v>
       </c>
       <c r="B11" t="n">
-        <v>57821</v>
+        <v>57817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,45 +1741,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126868067</v>
+        <v>126867857</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>699947</v>
+        <v>699822</v>
       </c>
       <c r="R12" t="n">
-        <v>7113090</v>
+        <v>7113408</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,29 +1826,25 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 20 st på liten yta</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1847,57 +1855,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126867857</v>
+        <v>126868067</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>699822</v>
+        <v>699947</v>
       </c>
       <c r="R13" t="n">
-        <v>7113408</v>
+        <v>7113090</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,25 +1928,29 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ca 20 st på liten yta</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1964,7 +1964,7 @@
         <v>126862664</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2065,7 +2065,7 @@
         <v>126864681</v>
       </c>
       <c r="B15" t="n">
-        <v>80121</v>
+        <v>80114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>126862622</v>
       </c>
       <c r="B16" t="n">
-        <v>80121</v>
+        <v>80114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2267,7 +2267,7 @@
         <v>126862590</v>
       </c>
       <c r="B17" t="n">
-        <v>57821</v>
+        <v>57817</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2377,45 +2377,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126868062</v>
+        <v>126867850</v>
       </c>
       <c r="B18" t="n">
-        <v>57821</v>
+        <v>98457</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>699845</v>
+        <v>699955</v>
       </c>
       <c r="R18" t="n">
-        <v>7113187</v>
+        <v>7113130</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,12 +2462,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2478,10 +2478,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126867850</v>
+        <v>126867848</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>98457</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>699955</v>
+        <v>699755</v>
       </c>
       <c r="R19" t="n">
-        <v>7113130</v>
+        <v>7113586</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,45 +2579,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126867848</v>
+        <v>126868062</v>
       </c>
       <c r="B20" t="n">
-        <v>98469</v>
+        <v>57817</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>699755</v>
+        <v>699845</v>
       </c>
       <c r="R20" t="n">
-        <v>7113586</v>
+        <v>7113187</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,12 +2664,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2680,10 +2680,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126864675</v>
+        <v>126863282</v>
       </c>
       <c r="B21" t="n">
-        <v>96700</v>
+        <v>91319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,21 +2691,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>699913</v>
+        <v>699958</v>
       </c>
       <c r="R21" t="n">
-        <v>7113203</v>
+        <v>7113052</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,12 +2765,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126863282</v>
+        <v>126862599</v>
       </c>
       <c r="B22" t="n">
-        <v>91330</v>
+        <v>80115</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2792,21 +2792,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>699958</v>
+        <v>699778</v>
       </c>
       <c r="R22" t="n">
-        <v>7113052</v>
+        <v>7113628</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,12 +2866,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2882,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126862599</v>
+        <v>126864675</v>
       </c>
       <c r="B23" t="n">
-        <v>80122</v>
+        <v>96689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2893,21 +2893,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>699778</v>
+        <v>699913</v>
       </c>
       <c r="R23" t="n">
-        <v>7113628</v>
+        <v>7113203</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2967,12 +2967,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2986,7 +2986,7 @@
         <v>126862624</v>
       </c>
       <c r="B24" t="n">
-        <v>80121</v>
+        <v>80114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3084,32 +3084,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126862598</v>
+        <v>126868058</v>
       </c>
       <c r="B25" t="n">
-        <v>98469</v>
+        <v>91319</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699820</v>
+        <v>699940</v>
       </c>
       <c r="R25" t="n">
-        <v>7113394</v>
+        <v>7113194</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3169,12 +3169,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3185,32 +3185,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126868058</v>
+        <v>126862598</v>
       </c>
       <c r="B26" t="n">
-        <v>91330</v>
+        <v>98457</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699940</v>
+        <v>699820</v>
       </c>
       <c r="R26" t="n">
-        <v>7113194</v>
+        <v>7113394</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3270,12 +3270,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3286,10 +3286,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126862627</v>
+        <v>126862669</v>
       </c>
       <c r="B27" t="n">
-        <v>80157</v>
+        <v>98353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3297,21 +3297,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699788</v>
+        <v>699879</v>
       </c>
       <c r="R27" t="n">
-        <v>7113541</v>
+        <v>7113265</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3387,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126862570</v>
+        <v>126867894</v>
       </c>
       <c r="B28" t="n">
-        <v>105471</v>
+        <v>98353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,34 +3398,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221725</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699830</v>
+        <v>699948</v>
       </c>
       <c r="R28" t="n">
-        <v>7113371</v>
+        <v>7113110</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,12 +3472,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3488,10 +3488,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126862669</v>
+        <v>126862570</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>105456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,21 +3499,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>221725</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699879</v>
+        <v>699830</v>
       </c>
       <c r="R29" t="n">
-        <v>7113265</v>
+        <v>7113371</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126867894</v>
+        <v>126862627</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>80150</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3600,34 +3600,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699948</v>
+        <v>699788</v>
       </c>
       <c r="R30" t="n">
-        <v>7113110</v>
+        <v>7113541</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3674,12 +3674,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3690,10 +3690,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126867883</v>
+        <v>126864689</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>82852</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3701,34 +3701,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699804</v>
+        <v>699933</v>
       </c>
       <c r="R31" t="n">
-        <v>7113653</v>
+        <v>7113088</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3769,18 +3769,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3791,10 +3792,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126864689</v>
+        <v>126867883</v>
       </c>
       <c r="B32" t="n">
-        <v>82859</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3802,34 +3803,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699933</v>
+        <v>699804</v>
       </c>
       <c r="R32" t="n">
-        <v>7113088</v>
+        <v>7113653</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,19 +3871,18 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3896,7 +3896,7 @@
         <v>126863288</v>
       </c>
       <c r="B33" t="n">
-        <v>91626</v>
+        <v>91615</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>126867886</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>126862623</v>
       </c>
       <c r="B35" t="n">
-        <v>80121</v>
+        <v>80114</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4196,10 +4196,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126863291</v>
+        <v>126867844</v>
       </c>
       <c r="B36" t="n">
-        <v>80121</v>
+        <v>57817</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4207,34 +4207,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699885</v>
+        <v>699887</v>
       </c>
       <c r="R36" t="n">
-        <v>7113259</v>
+        <v>7113380</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4281,12 +4281,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4297,10 +4297,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126867844</v>
+        <v>126863291</v>
       </c>
       <c r="B37" t="n">
-        <v>57821</v>
+        <v>80114</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4308,34 +4308,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699887</v>
+        <v>699885</v>
       </c>
       <c r="R37" t="n">
-        <v>7113380</v>
+        <v>7113259</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,12 +4382,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4398,27 +4398,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126862672</v>
+        <v>126867889</v>
       </c>
       <c r="B38" t="n">
-        <v>80156</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4429,14 +4429,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699843</v>
+        <v>699818</v>
       </c>
       <c r="R38" t="n">
-        <v>7113335</v>
+        <v>7113415</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4483,12 +4483,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4499,10 +4499,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126868055</v>
+        <v>126862672</v>
       </c>
       <c r="B39" t="n">
-        <v>91295</v>
+        <v>80149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699981</v>
+        <v>699843</v>
       </c>
       <c r="R39" t="n">
-        <v>7113021</v>
+        <v>7113335</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4600,45 +4600,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126867889</v>
+        <v>126868055</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>91284</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699818</v>
+        <v>699981</v>
       </c>
       <c r="R40" t="n">
-        <v>7113415</v>
+        <v>7113021</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4685,12 +4685,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4704,7 +4704,7 @@
         <v>126867887</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4802,45 +4802,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126867884</v>
+        <v>126862595</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>80143</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699877</v>
+        <v>699848</v>
       </c>
       <c r="R42" t="n">
-        <v>7113569</v>
+        <v>7113330</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4887,12 +4887,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4903,45 +4903,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126862595</v>
+        <v>126867884</v>
       </c>
       <c r="B43" t="n">
-        <v>80150</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699848</v>
+        <v>699877</v>
       </c>
       <c r="R43" t="n">
-        <v>7113330</v>
+        <v>7113569</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4988,12 +4988,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5007,7 +5007,7 @@
         <v>126862628</v>
       </c>
       <c r="B44" t="n">
-        <v>80121</v>
+        <v>80114</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5108,7 +5108,7 @@
         <v>126862671</v>
       </c>
       <c r="B45" t="n">
-        <v>98365</v>
+        <v>98353</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5206,45 +5206,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126867851</v>
+        <v>126862620</v>
       </c>
       <c r="B46" t="n">
-        <v>98469</v>
+        <v>80114</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699963</v>
+        <v>699885</v>
       </c>
       <c r="R46" t="n">
-        <v>7113120</v>
+        <v>7113266</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5291,12 +5291,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5307,10 +5307,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126862659</v>
+        <v>126867851</v>
       </c>
       <c r="B47" t="n">
-        <v>75125</v>
+        <v>98457</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,34 +5318,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6439</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699845</v>
+        <v>699963</v>
       </c>
       <c r="R47" t="n">
-        <v>7113325</v>
+        <v>7113120</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,12 +5392,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5408,32 +5408,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126862620</v>
+        <v>126862581</v>
       </c>
       <c r="B48" t="n">
-        <v>80121</v>
+        <v>91284</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>699885</v>
+        <v>699816</v>
       </c>
       <c r="R48" t="n">
-        <v>7113266</v>
+        <v>7113390</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5509,10 +5509,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126862581</v>
+        <v>126862659</v>
       </c>
       <c r="B49" t="n">
-        <v>91295</v>
+        <v>75118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5520,21 +5520,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>6439</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>699816</v>
+        <v>699845</v>
       </c>
       <c r="R49" t="n">
-        <v>7113390</v>
+        <v>7113325</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5613,7 +5613,7 @@
         <v>126864677</v>
       </c>
       <c r="B50" t="n">
-        <v>91330</v>
+        <v>91319</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>126867890</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>126864676</v>
       </c>
       <c r="B52" t="n">
-        <v>91295</v>
+        <v>91284</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5913,10 +5913,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126862568</v>
+        <v>126863289</v>
       </c>
       <c r="B53" t="n">
-        <v>105471</v>
+        <v>97314</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5924,21 +5924,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>699772</v>
+        <v>699799</v>
       </c>
       <c r="R53" t="n">
-        <v>7113578</v>
+        <v>7113391</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5998,12 +5998,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6014,10 +6014,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126863289</v>
+        <v>126862568</v>
       </c>
       <c r="B54" t="n">
-        <v>97325</v>
+        <v>105456</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6025,21 +6025,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6049,10 +6049,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>699799</v>
+        <v>699772</v>
       </c>
       <c r="R54" t="n">
-        <v>7113391</v>
+        <v>7113578</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6099,12 +6099,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6118,7 +6118,7 @@
         <v>126863287</v>
       </c>
       <c r="B55" t="n">
-        <v>91626</v>
+        <v>91615</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>126867837</v>
       </c>
       <c r="B56" t="n">
-        <v>105473</v>
+        <v>105456</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>126864684</v>
       </c>
       <c r="B57" t="n">
-        <v>78424</v>
+        <v>78415</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -6320,7 +6320,7 @@
         <v>126864684</v>
       </c>
       <c r="B57" t="n">
-        <v>78424</v>
+        <v>78729</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -6320,7 +6320,7 @@
         <v>126864684</v>
       </c>
       <c r="B57" t="n">
-        <v>78729</v>
+        <v>78730</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -6320,7 +6320,7 @@
         <v>126864684</v>
       </c>
       <c r="B57" t="n">
-        <v>78734</v>
+        <v>78735</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1964541</v>
+        <v>126864675</v>
       </c>
       <c r="B2" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillgodberg, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699962.3294355422</v>
+        <v>699913</v>
       </c>
       <c r="R2" t="n">
-        <v>7113213.131284747</v>
+        <v>7113203</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-09-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,44 +756,30 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Sälg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Alexandra Astafourova</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1964540</v>
+        <v>126863287</v>
       </c>
       <c r="B3" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,34 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillgodberg, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699880.8385152917</v>
+        <v>699922</v>
       </c>
       <c r="R3" t="n">
-        <v>7113257.870852905</v>
+        <v>7113084</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2010-09-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2010-09-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,39 +857,30 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Sälg</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126380574</v>
+        <v>126863288</v>
       </c>
       <c r="B4" t="n">
-        <v>91263</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,34 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Inre Öreström, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699818</v>
+        <v>699939</v>
       </c>
       <c r="R4" t="n">
-        <v>7113393</v>
+        <v>7113199</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,41 +958,30 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126864688</v>
+        <v>126863282</v>
       </c>
       <c r="B5" t="n">
-        <v>82859</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699884</v>
+        <v>699958</v>
       </c>
       <c r="R5" t="n">
-        <v>7113179</v>
+        <v>7113052</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,19 +1057,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1139,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126868059</v>
+        <v>126864677</v>
       </c>
       <c r="B6" t="n">
-        <v>91330</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699956</v>
+        <v>699961</v>
       </c>
       <c r="R6" t="n">
-        <v>7113052</v>
+        <v>7113050</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,12 +1164,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1240,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126862626</v>
+        <v>126868057</v>
       </c>
       <c r="B7" t="n">
-        <v>80121</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>699893</v>
+        <v>699944</v>
       </c>
       <c r="R7" t="n">
-        <v>7113185</v>
+        <v>7113181</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,12 +1265,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1341,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126862625</v>
+        <v>126868058</v>
       </c>
       <c r="B8" t="n">
-        <v>80121</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>699832</v>
+        <v>699940</v>
       </c>
       <c r="R8" t="n">
-        <v>7113407</v>
+        <v>7113194</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,12 +1366,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1442,32 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126862596</v>
+        <v>126868059</v>
       </c>
       <c r="B9" t="n">
-        <v>99092</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222302</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1477,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>699829</v>
+        <v>699956</v>
       </c>
       <c r="R9" t="n">
-        <v>7113383</v>
+        <v>7113052</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,12 +1467,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1543,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126868057</v>
+        <v>126864688</v>
       </c>
       <c r="B10" t="n">
-        <v>91330</v>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>699944</v>
+        <v>699884</v>
       </c>
       <c r="R10" t="n">
-        <v>7113181</v>
+        <v>7113179</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,18 +1562,19 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1644,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126850606</v>
+        <v>126864689</v>
       </c>
       <c r="B11" t="n">
-        <v>57821</v>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,37 +1596,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nydala, Nydala, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>699845</v>
+        <v>699933</v>
       </c>
       <c r="R11" t="n">
-        <v>7113169</v>
+        <v>7113088</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1723,50 +1664,55 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Alexandra Astafourova</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126868067</v>
+        <v>126862599</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1722,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>699947</v>
+        <v>699778</v>
       </c>
       <c r="R12" t="n">
-        <v>7113090</v>
+        <v>7113628</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,11 +1760,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 20 st på liten yta</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1831,12 +1772,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1847,57 +1788,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126867857</v>
+        <v>126862581</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>699822</v>
+        <v>699816</v>
       </c>
       <c r="R13" t="n">
-        <v>7113408</v>
+        <v>7113390</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,19 +1867,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1961,32 +1889,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126862664</v>
+        <v>126864676</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1996,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>699735</v>
+        <v>699986</v>
       </c>
       <c r="R14" t="n">
-        <v>7113552</v>
+        <v>7113023</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,12 +1974,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2062,32 +1990,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126864681</v>
+        <v>126868055</v>
       </c>
       <c r="B15" t="n">
-        <v>80121</v>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2097,10 +2025,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>699880</v>
+        <v>699981</v>
       </c>
       <c r="R15" t="n">
-        <v>7113259</v>
+        <v>7113021</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,12 +2075,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2163,32 +2091,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126862622</v>
+        <v>126862664</v>
       </c>
       <c r="B16" t="n">
-        <v>80121</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2126,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>699782</v>
+        <v>699735</v>
       </c>
       <c r="R16" t="n">
-        <v>7113622</v>
+        <v>7113552</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2181,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2264,57 +2192,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126862590</v>
+        <v>126867883</v>
       </c>
       <c r="B17" t="n">
-        <v>57821</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>699877</v>
+        <v>699804</v>
       </c>
       <c r="R17" t="n">
-        <v>7113231</v>
+        <v>7113653</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,12 +2277,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2377,45 +2293,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126868062</v>
+        <v>126867884</v>
       </c>
       <c r="B18" t="n">
-        <v>57821</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>699845</v>
+        <v>699877</v>
       </c>
       <c r="R18" t="n">
-        <v>7113187</v>
+        <v>7113569</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,12 +2378,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2478,32 +2394,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126867850</v>
+        <v>126867886</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2513,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>699955</v>
+        <v>699878</v>
       </c>
       <c r="R19" t="n">
-        <v>7113130</v>
+        <v>7113551</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,32 +2495,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126867848</v>
+        <v>126867887</v>
       </c>
       <c r="B20" t="n">
-        <v>98469</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2614,10 +2530,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>699755</v>
+        <v>699826</v>
       </c>
       <c r="R20" t="n">
-        <v>7113586</v>
+        <v>7113435</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2680,45 +2596,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126864675</v>
+        <v>126867889</v>
       </c>
       <c r="B21" t="n">
-        <v>96700</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>699913</v>
+        <v>699818</v>
       </c>
       <c r="R21" t="n">
-        <v>7113203</v>
+        <v>7113415</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,12 +2681,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2781,45 +2697,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126863282</v>
+        <v>126867890</v>
       </c>
       <c r="B22" t="n">
-        <v>91330</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>699958</v>
+        <v>699832</v>
       </c>
       <c r="R22" t="n">
-        <v>7113052</v>
+        <v>7113381</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,12 +2782,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2882,32 +2798,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126862599</v>
+        <v>126864684</v>
       </c>
       <c r="B23" t="n">
-        <v>80122</v>
+        <v>78774</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6436</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2833,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>699778</v>
+        <v>699958</v>
       </c>
       <c r="R23" t="n">
-        <v>7113628</v>
+        <v>7113051</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2961,18 +2877,19 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2983,32 +2900,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126862624</v>
+        <v>126862659</v>
       </c>
       <c r="B24" t="n">
-        <v>80121</v>
+        <v>83290</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3018,10 +2935,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>699857</v>
+        <v>699845</v>
       </c>
       <c r="R24" t="n">
-        <v>7113431</v>
+        <v>7113325</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3073,7 +2990,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3084,45 +3001,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126862598</v>
+        <v>1964539</v>
       </c>
       <c r="B25" t="n">
-        <v>98469</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberg, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699820</v>
+        <v>699974</v>
       </c>
       <c r="R25" t="n">
-        <v>7113394</v>
+        <v>7113214</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3149,12 +3066,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2010-09-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2010-09-08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3165,30 +3082,39 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Sälg</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Hällström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Hällström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126868058</v>
+        <v>1964540</v>
       </c>
       <c r="B26" t="n">
-        <v>91330</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3196,34 +3122,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberg, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699940</v>
+        <v>699881</v>
       </c>
       <c r="R26" t="n">
-        <v>7113194</v>
+        <v>7113258</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,12 +3176,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2010-09-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2010-09-08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3266,65 +3192,74 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Sälg</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Hällström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Hällström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126862627</v>
+        <v>1964541</v>
       </c>
       <c r="B27" t="n">
-        <v>80157</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberg, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699788</v>
+        <v>699962</v>
       </c>
       <c r="R27" t="n">
-        <v>7113541</v>
+        <v>7113213</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3351,12 +3286,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2010-09-08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2010-09-08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3367,68 +3302,77 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AN27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Sälg</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Hällström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Hällström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126862570</v>
+        <v>126851690</v>
       </c>
       <c r="B28" t="n">
-        <v>105471</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Nydala, Nydala, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699830</v>
+        <v>699975</v>
       </c>
       <c r="R28" t="n">
-        <v>7113371</v>
+        <v>7113150</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3472,48 +3416,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126862669</v>
+        <v>126862620</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3523,10 +3463,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699879</v>
+        <v>699885</v>
       </c>
       <c r="R29" t="n">
-        <v>7113265</v>
+        <v>7113266</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3589,45 +3529,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126867894</v>
+        <v>126862622</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699948</v>
+        <v>699782</v>
       </c>
       <c r="R30" t="n">
-        <v>7113110</v>
+        <v>7113622</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3674,12 +3614,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3690,10 +3630,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126867883</v>
+        <v>126862623</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3701,34 +3641,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699804</v>
+        <v>699773</v>
       </c>
       <c r="R31" t="n">
-        <v>7113653</v>
+        <v>7113587</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3775,12 +3715,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3791,10 +3731,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126864689</v>
+        <v>126862624</v>
       </c>
       <c r="B32" t="n">
-        <v>82859</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3802,21 +3742,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3826,10 +3766,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699933</v>
+        <v>699857</v>
       </c>
       <c r="R32" t="n">
-        <v>7113088</v>
+        <v>7113431</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,19 +3810,18 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3893,10 +3832,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126863288</v>
+        <v>126862625</v>
       </c>
       <c r="B33" t="n">
-        <v>91626</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3904,21 +3843,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3928,10 +3867,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699939</v>
+        <v>699832</v>
       </c>
       <c r="R33" t="n">
-        <v>7113199</v>
+        <v>7113407</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3978,12 +3917,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3994,10 +3933,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126867886</v>
+        <v>126862626</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4005,34 +3944,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699878</v>
+        <v>699893</v>
       </c>
       <c r="R34" t="n">
-        <v>7113551</v>
+        <v>7113185</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4079,12 +4018,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4095,10 +4034,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126862623</v>
+        <v>126862628</v>
       </c>
       <c r="B35" t="n">
-        <v>80121</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4130,10 +4069,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699773</v>
+        <v>699783</v>
       </c>
       <c r="R35" t="n">
-        <v>7113587</v>
+        <v>7113533</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4199,7 +4138,7 @@
         <v>126863291</v>
       </c>
       <c r="B36" t="n">
-        <v>80121</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4297,10 +4236,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126867844</v>
+        <v>126864681</v>
       </c>
       <c r="B37" t="n">
-        <v>57821</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4308,34 +4247,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699887</v>
+        <v>699880</v>
       </c>
       <c r="R37" t="n">
-        <v>7113380</v>
+        <v>7113259</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,12 +4321,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4398,10 +4337,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126862672</v>
+        <v>126862595</v>
       </c>
       <c r="B38" t="n">
-        <v>80156</v>
+        <v>80461</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4409,21 +4348,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4433,10 +4372,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699843</v>
+        <v>699848</v>
       </c>
       <c r="R38" t="n">
-        <v>7113335</v>
+        <v>7113330</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4488,7 +4427,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4499,10 +4438,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126868055</v>
+        <v>126862672</v>
       </c>
       <c r="B39" t="n">
-        <v>91295</v>
+        <v>80467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4510,21 +4449,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4534,10 +4473,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699981</v>
+        <v>699843</v>
       </c>
       <c r="R39" t="n">
-        <v>7113021</v>
+        <v>7113335</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4584,12 +4523,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4600,45 +4539,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126867889</v>
+        <v>126862627</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>80468</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699818</v>
+        <v>699788</v>
       </c>
       <c r="R40" t="n">
-        <v>7113415</v>
+        <v>7113541</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4685,12 +4624,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4701,10 +4640,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126867887</v>
+        <v>126851665</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4712,37 +4651,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Nydala, Nydala, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699826</v>
+        <v>699976</v>
       </c>
       <c r="R41" t="n">
-        <v>7113435</v>
+        <v>7113152</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4772,6 +4716,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4794,18 +4743,14 @@
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126867884</v>
+        <v>126850606</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>58114</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4813,37 +4758,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Nydala, Nydala, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699877</v>
+        <v>699845</v>
       </c>
       <c r="R42" t="n">
-        <v>7113569</v>
+        <v>7113169</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4895,53 +4840,61 @@
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126862595</v>
+        <v>126862590</v>
       </c>
       <c r="B43" t="n">
-        <v>80150</v>
+        <v>58114</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699848</v>
+        <v>699877</v>
       </c>
       <c r="R43" t="n">
-        <v>7113330</v>
+        <v>7113231</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4993,7 +4946,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5004,10 +4957,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126862628</v>
+        <v>126867844</v>
       </c>
       <c r="B44" t="n">
-        <v>80121</v>
+        <v>58114</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5015,34 +4968,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699783</v>
+        <v>699887</v>
       </c>
       <c r="R44" t="n">
-        <v>7113533</v>
+        <v>7113380</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5089,12 +5042,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5105,32 +5058,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126862671</v>
+        <v>126868062</v>
       </c>
       <c r="B45" t="n">
-        <v>98365</v>
+        <v>58114</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699946</v>
+        <v>699845</v>
       </c>
       <c r="R45" t="n">
-        <v>7113098</v>
+        <v>7113187</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5190,12 +5143,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5206,10 +5159,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126867851</v>
+        <v>126862669</v>
       </c>
       <c r="B46" t="n">
-        <v>98469</v>
+        <v>99035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5217,34 +5170,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699963</v>
+        <v>699879</v>
       </c>
       <c r="R46" t="n">
-        <v>7113120</v>
+        <v>7113265</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5291,12 +5244,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5307,10 +5260,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126862659</v>
+        <v>126862671</v>
       </c>
       <c r="B47" t="n">
-        <v>75125</v>
+        <v>99035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,21 +5271,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6439</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5342,10 +5295,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699845</v>
+        <v>699946</v>
       </c>
       <c r="R47" t="n">
-        <v>7113325</v>
+        <v>7113098</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5397,7 +5350,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5408,45 +5361,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126862620</v>
+        <v>126867894</v>
       </c>
       <c r="B48" t="n">
-        <v>80121</v>
+        <v>99035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>699885</v>
+        <v>699948</v>
       </c>
       <c r="R48" t="n">
-        <v>7113266</v>
+        <v>7113110</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5493,12 +5446,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5509,10 +5462,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126862581</v>
+        <v>126868067</v>
       </c>
       <c r="B49" t="n">
-        <v>91295</v>
+        <v>99035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5520,21 +5473,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5544,10 +5497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>699816</v>
+        <v>699947</v>
       </c>
       <c r="R49" t="n">
-        <v>7113390</v>
+        <v>7113090</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5582,6 +5535,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ca 20 st på liten yta</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5594,12 +5552,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5610,48 +5568,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126864677</v>
+        <v>126851566</v>
       </c>
       <c r="B50" t="n">
-        <v>91330</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Nydala, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>699961</v>
+        <v>699979</v>
       </c>
       <c r="R50" t="n">
-        <v>7113050</v>
+        <v>7113129</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5695,64 +5653,69 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126867890</v>
+        <v>126851719</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Nydala, Nydala, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>699832</v>
+        <v>699994</v>
       </c>
       <c r="R51" t="n">
-        <v>7113381</v>
+        <v>7113172</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5804,53 +5767,61 @@
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126864676</v>
+        <v>126867857</v>
       </c>
       <c r="B52" t="n">
-        <v>91295</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>699986</v>
+        <v>699822</v>
       </c>
       <c r="R52" t="n">
-        <v>7113023</v>
+        <v>7113408</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5891,18 +5862,19 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5916,7 +5888,7 @@
         <v>126862568</v>
       </c>
       <c r="B53" t="n">
-        <v>105471</v>
+        <v>106229</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6003,7 +5975,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6014,10 +5986,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126863289</v>
+        <v>126862570</v>
       </c>
       <c r="B54" t="n">
-        <v>97325</v>
+        <v>106229</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6025,21 +5997,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6049,10 +6021,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>699799</v>
+        <v>699830</v>
       </c>
       <c r="R54" t="n">
-        <v>7113391</v>
+        <v>7113371</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6099,12 +6071,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6115,45 +6087,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126863287</v>
+        <v>126867837</v>
       </c>
       <c r="B55" t="n">
-        <v>91626</v>
+        <v>106229</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>221725</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>699922</v>
+        <v>699874</v>
       </c>
       <c r="R55" t="n">
-        <v>7113084</v>
+        <v>7113403</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6200,12 +6172,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6216,10 +6188,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126867837</v>
+        <v>126863289</v>
       </c>
       <c r="B56" t="n">
-        <v>105473</v>
+        <v>97983</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6227,34 +6199,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>699874</v>
+        <v>699799</v>
       </c>
       <c r="R56" t="n">
-        <v>7113403</v>
+        <v>7113391</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6301,12 +6273,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6317,10 +6289,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126864684</v>
+        <v>126862598</v>
       </c>
       <c r="B57" t="n">
-        <v>78735</v>
+        <v>99140</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6328,21 +6300,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6436</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6352,10 +6324,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>699958</v>
+        <v>699820</v>
       </c>
       <c r="R57" t="n">
-        <v>7113051</v>
+        <v>7113394</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6396,22 +6368,425 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126867848</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>699755</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7113586</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126867850</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>699955</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7113130</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126867851</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>699963</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7113120</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126862596</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99771</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222302</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Spädstarr</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carex disperma</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Dewey</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lillgoberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>699829</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7113383</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>

--- a/artfynd/A 33362-2024 artfynd.xlsx
+++ b/artfynd/A 33362-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864675</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126863287</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126863288</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126863282</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864677</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868057</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868058</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868059</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1582,6 +1627,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864688</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1684,6 +1734,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864689</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1785,6 +1840,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862599</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1886,6 +1946,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862581</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1987,6 +2052,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864676</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2088,6 +2158,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868055</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2189,6 +2264,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862664</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2290,6 +2370,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867883</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2391,6 +2476,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867884</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2492,6 +2582,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867886</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2593,6 +2688,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867887</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2694,6 +2794,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867889</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2795,6 +2900,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867890</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2897,6 +3007,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864684</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2998,6 +3113,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862659</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3108,6 +3228,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964539</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3218,6 +3343,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964540</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3328,6 +3458,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964541</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3425,6 +3560,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126851690</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3526,6 +3666,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862620</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3627,6 +3772,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862622</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3728,6 +3878,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862623</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3829,6 +3984,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862624</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3930,6 +4090,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862625</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4031,6 +4196,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862626</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4132,6 +4302,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862628</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4233,6 +4408,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126863291</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4334,6 +4514,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864681</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4435,6 +4620,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862595</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4536,6 +4726,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862672</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4637,6 +4832,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862627</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4744,6 +4944,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126851665</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4841,6 +5046,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126850606</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4954,6 +5164,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862590</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5055,6 +5270,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867844</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5156,6 +5376,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868062</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5257,6 +5482,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862669</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5358,6 +5588,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862671</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5459,6 +5694,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867894</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5565,6 +5805,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868067</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5662,6 +5907,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126851566</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5768,6 +6018,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126851719</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5882,6 +6137,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867857</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5983,6 +6243,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862568</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6084,6 +6349,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862570</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6185,6 +6455,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867837</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6286,6 +6561,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126863289</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6387,6 +6667,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862598</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6488,6 +6773,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867848</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6589,6 +6879,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867850</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6690,6 +6985,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867851</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6791,8 +7091,75 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862596</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>